--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:G287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10323,6 +10323,146 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/789524-bizdev-igaming/</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>BizDev (iGaming)</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/789524-bizdev-igaming/</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833582-senior-lead-manual-qa-engineer/</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Senior/Lead Manual QA Engineer</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833582-senior-lead-manual-qa-engineer/</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833580-senior-lead-manual-qa-engineer/</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Senior/Lead Manual QA Engineer</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833580-senior-lead-manual-qa-engineer/</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>linkedin_abcc1e141bc7</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Senior Growth &amp; BI Analyst</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Globaldev Group</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>https://ua.linkedin.com/jobs/view/senior-growth-bi-analyst-at-globaldev-group-4432551223</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10463,6 +10463,181 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833585-senior-fullstack-software-engineer/</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Senior FullStack Software Engineer</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833585-senior-fullstack-software-engineer/</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>2</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833587-intern-integration-analyst-providnii-bank-ukr/</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Intern Integration Analyst (Провідний банк України)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833587-intern-integration-analyst-providnii-bank-ukr/</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833588-senior-system-analyst/</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Senior System Analyst</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833588-senior-system-analyst/</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>2</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833584-menedzher-po-roboti-z-kliientami/</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Менеджер по роботі з клієнтами</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833584-menedzher-po-roboti-z-kliientami/</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833583-ml-engineer/</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833583-ml-engineer/</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G292"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10638,6 +10638,216 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>linkedin_2e1429bb19f3</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Director of Data Strategy &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Purchasing Platform, Inc.</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-of-data-strategy-analytics-at-purchasing-platform-inc-4432431272</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>6</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>linkedin_2c02cce1c894</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Director of Data Analytics</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>PRI Technology</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-of-data-analytics-at-pri-technology-4432269862</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>2</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>linkedin_7875a5f7978f</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Director, B2B Data Strategy &amp; Revenue Analytics</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Wpromote</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/director-b2b-data-strategy-revenue-analytics-at-wpromote-4413052249</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>6</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>linkedin_4640154b24fa</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Growth</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Collectors</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/analytics-manager-growth-at-collectors-4368568096</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>3</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>linkedin_ecb41d74b8fc</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Marketplace</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Collectors</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/analytics-manager-marketplace-at-collectors-4400777695</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>3</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>linkedin_9ca3bdd8f77a</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Associate Director, Real World Data Strategy</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-director-real-world-data-strategy-at-bristol-myers-squibb-4422139900</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>4</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10848,6 +10848,251 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>N-iX_4de7a7307034</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Data Analyst (with Power BI)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4892381101?gh_jid=4892381101</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>N-iX_0e1e168dc89d</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst (Marketing Performance)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4861106101?gh_jid=4861106101</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>4</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>N-iX_558f7a5c5707</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Middle Data Analyst</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4885308101?gh_jid=4885308101</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>2</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>N-iX_afaecfa4138b</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle Data Analyst (with dbt) </t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4885307101?gh_jid=4885307101</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>N-iX_2151154b4ba4</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle Data Analyst (with dbt) </t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4891599101?gh_jid=4891599101</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>1</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>tg_5bb869e1f9cc</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>А що там по ментальному здоровʼю? 🤔 Чи правда, що роботодавцю не має бути діла до вашого психологічного стану і це повні</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>@workado_jobs</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>https://t.me/workado_jobs/7061</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Telegram/workado_jobs</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>tg_d117ada6a8b1</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>↗️ ToDo — todo.ltd 👨‍💻 Бізнес-аналітик (впровадження Odoo) 🚀 Дистанційна робота ✅ Повна зайнятість. Також готові взяти с</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>@ymlnvjobs</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>https://t.me/ymlnvjobs/2505</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Telegram/ymlnvjobs</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G305"/>
+  <dimension ref="A1:G306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11093,6 +11093,41 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>weworkremotely_53a5edbe816b</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Data Analyst/ Curam9dAHU TechnologiesFully Remote - USFull-TimeAnywhere in the World</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/ahu-technologies-data-analyst-curam</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Weworkremotely</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>2</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11128,6 +11128,41 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/zagoriy-foundation/vacancies/357911/?1782298948</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Impact &amp;amp; Data Analyst в Zagoriy Foundation, Київ</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zagoriy-foundation/vacancies/357911/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11163,6 +11163,41 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/globaldevgroup/vacancies/363367/?1782299416</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Senior Growth &amp;amp; BI Analyst в Globaldev Group, віддалено</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/globaldevgroup/vacancies/363367/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +1394,1670 @@
       <c r="F31" t="inlineStr">
         <is>
           <t>2026-06-24 11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ELEKS_b8e7253ea79d</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Solution Business Analyst, UK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ELEKS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/eleks/a9fc0cce-3f51-469b-913d-a1cb0c995ed9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ELEKS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>N-iX_c251e31a05ae</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Middle Business Analyst with AI exp</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4847582101?gh_jid=4847582101</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>N-iX_36e2002dd910</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle HRMS Configurator/People Analyst </t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4870415101?gh_jid=4870415101</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>N-iX_9100095d94e8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Middle/Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4881669101?gh_jid=4881669101</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>N-iX_e48cf6d577af</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Middle/Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4896632101?gh_jid=4896632101</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>N-iX_23f73ba2c596</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Senior Business/System Analyst</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4787051101?gh_jid=4787051101</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Playtika_a2f7c151289d</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4660259101</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Playtika_7c2e28897e3b</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Games R&amp;D - R&amp;D Team Lead</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4880515101</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Playtika_bc5ddbcbc01b</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing Strategy Manager - Maternity Leave Replacement </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4860542101</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/dripify/vacancies/363431/?1782309979</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Marketing Data Analyst (part-time) в Dripify, віддалено</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/dripify/vacancies/363431/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/truelabel/vacancies/352602/?1782309847</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Head of Analytics в TrueLabel, віддалено</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/truelabel/vacancies/352602/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/starlightmedia/vacancies/363423/?1782308728</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Старший(а) фахівець(чиня) з веб-аналітики та ефективності digital-платформ в Starlight Media, $1200–1700, віддалено</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/starlightmedia/vacancies/363423/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/natsionalna-suspilna-teleradiokompaniya-ukrajini/vacancies/363305/?1782284390</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Медіа-аналітик/-киня в Національна суспільна телерадіокомпанія України, Київ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/natsionalna-suspilna-teleradiokompaniya-ukrajini/vacancies/363305/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/a4362/vacancies/353759/?1782283303</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Junior Cyber Security Analyst L1 в A4362, $500–1200, Одеса</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/a4362/vacancies/353759/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/unicsoft/vacancies/363294/?1782248198</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IT Business Analyst (AI &amp;amp; Automation) — Helpware в Unicsoft, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/unicsoft/vacancies/363294/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nda-recruitment/vacancies/363280/?1782232761</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>QA Lead — Analyst (Complex ERP Systems) в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363280/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/mticket/vacancies/358242/?1782224788</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Business Analyst в Mticket, віддалено</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mticket/vacancies/358242/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/boosta/vacancies/363254/?1782224282</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Product Web Analyst | Edlight в Boosta, віддалено</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/boosta/vacancies/363254/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/squad/vacancies/363230/?1782220666</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sales Intelligence Analyst в SQUAD, Київ, Львів, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/squad/vacancies/363230/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nda-recruitment/vacancies/363200/?1782216713</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Threat Intelligence Analyst в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363200/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/ralabs/vacancies/363197/?1782216237</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Business Analyst (Defense domain) в Ralabs, віддалено</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ralabs/vacancies/363197/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/vodafone-ukraine/vacancies/356477/?1781699369</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Head of Big Data Products в Vodafone Україна, Київ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/vodafone-ukraine/vacancies/356477/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/mod-of-ukraine/vacancies/346866/?1780666933</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Head of Data Analytics в Міністерство оборони України, Київ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mod-of-ukraine/vacancies/346866/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/356052/?1780312848</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Head of Data Analytics &amp;amp; Strategy в ROZETKA, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/356052/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/universal-bank/vacancies/360184/?1780303160</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Head of Data Office в JSC Universal Bank, Київ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/universal-bank/vacancies/360184/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/upg/vacancies/363048/?1782137783</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Head of Analytics в UPG, віддалено</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/upg/vacancies/363048/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/m32/vacancies/357782/?1781533615</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Head of Analytics в M32, віддалено</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/m32/vacancies/357782/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/golden-staff/vacancies/361550/?1781074468</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Старший аналітик / Head of Commercial Analytics/Керівник напряму комерційної аналітики/бронювання/FMCG в GOLDEN STAFF, $1600–2000, Київ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/golden-staff/vacancies/361550/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/zone3000/vacancies/349277/?1782200599</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Finance Analyst in Global BI Team (#1123) в ZONE3000, віддалено</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zone3000/vacancies/349277/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/blagodiina-organizatsiya-blagodiinii-fond-spilnota-sternenka/vacancies/358820/?1782113107</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst в Благодійна Організація Благодійний Фонд "Спільнота Стерненка", Київ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/blagodiina-organizatsiya-blagodiinii-fond-spilnota-sternenka/vacancies/358820/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/boosters-product-team/vacancies/352931/?1781627130</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Middle/Senior Data Analyst в BOOSTERS - Product Team, віддалено</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/boosters-product-team/vacancies/352931/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/association-of-ukrainian-defense-manufacturers/vacancies/362306/?1781603360</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Lead Product/Data Analyst в Association of Ukrainian Defense Manufacturers, $1500–2000, Київ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/association-of-ukrainian-defense-manufacturers/vacancies/362306/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/king-group/vacancies/362284/?1781600385</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Data Analyst (Performance Marketing Team) в King Group, Київ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/king-group/vacancies/362284/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/uklon/vacancies/351376/?1780045503</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Data Analytics Lead в Uklon, Київ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/uklon/vacancies/351376/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/828570-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/828570-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/827449-mapping-and-transition-tables-analyst/</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mapping and Transition Tables Analyst</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827449-mapping-and-transition-tables-analyst/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/827044-data-engineer-analyst-gcp/</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Data Engineer/Analyst (GCP)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827044-data-engineer-analyst-gcp/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/828573-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/828573-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833704-hr-analyst/</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HR Analyst</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833704-hr-analyst/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833696-ice-hockey-analyst/</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833696-ice-hockey-analyst/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833671-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик / Фінансист</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833671-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833670-finansovii-analitik-mizhnarodni-rinki-kapital/</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик (міжнародні ринки капіталу, навчання)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833670-finansovii-analitik-mizhnarodni-rinki-kapital/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833657-risk-operations-analyst-igaming-antifraud/</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Risk Operations Analyst/IGaming/Antifraud</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833657-risk-operations-analyst-igaming-antifraud/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833663-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833663-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833549-bi-analyst-data-engineer/</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BI Analyst / Data Engineer</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833549-bi-analyst-data-engineer/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833000-head-of-data/</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Head of Data</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833000-head-of-data/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>tg_82cd07dd71ac</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bonus Marketing Manager (Trainee) SoftSvit — продуктова IT компанія, яка створює та просуває власні веб-проєкти. Шукаємо</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>@Space_Job</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://t.me/Space_Job/2977</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Telegram/Space_Job</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>wwr_7e2ec65a9a86</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Workday Financials Analyst Consultant (Global Delivery Center)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Collaborative Solutions</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/collaborative-solutions-workday-financials-analyst-consultant-global-delivery-center</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>wwr_9595c7047f20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Business &amp; CRM Analyst | Remote</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sonova International</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/sonova-international-business-crm-analyst-remote-1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>wwr_53a5edbe816b</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Data Analyst/ Curam</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AHU Technologies</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/ahu-technologies-data-analyst-curam</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>wwr_3e97d7ce706a</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (w/m/d) für SaaS und On-Premises Lösungen</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Septeo CNEE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/septeo-cnee-product-marketing-manager-w-m-d-fur-saas-und-on-premises-losungen</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>wwr_f2d70bba68d6</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Elite Software Automation</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/elite-software-automation-business-analyst-2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
         </is>
       </c>
     </row>
@@ -1408,7 +3072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -2386,6 +4050,1670 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Solution Business Analyst, UK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ELEKS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ELEKS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/eleks/a9fc0cce-3f51-469b-913d-a1cb0c995ed9</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ELEKS Business Analysis Office is looking for a Solution Business Analyst in the United Kingdom.   ABOUT PROJECT Choosing to work as a dedicated pre-sales Business Analyst at ELEKS in the UK can be a strong career move for both professional, and personal reasons; it’s an exciting opportunity to gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Middle Business Analyst with AI exp</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4847582101?gh_jid=4847582101</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;&amp;lt;strong&amp;gt;N-iX &amp;lt;/strong&amp;gt;is seeking an experienced and highly skilled &amp;lt;strong&amp;gt;Middle Business Analyst &amp;lt;/strong&amp;gt;to join our team in a leading pharmaceutical company. This role will focus on supporting data-driven and AI-powered initiatives that enhance decision-making, o</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle HRMS Configurator/People Analyst </t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4870415101?gh_jid=4870415101</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;N-iX is a software development service company that helps businesses across the globe develop successful software products. Founded in 2002, N-iX has come a long way and increased its presence in nine countries -&amp;amp;nbsp; Poland, Romania, Ukraine, Bulgaria, Sweden, Malta, the UK, the US, a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Middle/Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4881669101?gh_jid=4881669101</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;We are looking for a&amp;lt;strong&amp;gt; Middle/Senior Business Analyst&amp;lt;/strong&amp;gt; to join our team.&amp;lt;/p&amp;gt; &amp;lt;ul&amp;gt; &amp;lt;li&amp;gt; &amp;lt;p&amp;gt;&amp;lt;strong&amp;gt;Responsibilities:&amp;lt;/strong&amp;gt;&amp;lt;/p&amp;gt; &amp;lt;/li&amp;gt; &amp;lt;li&amp;gt;3+ years of experience as a Business Analyst in IT or business units&amp;lt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Middle/Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4896632101?gh_jid=4896632101</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;lt;p&amp;gt;&amp;lt;strong&amp;gt;About the Client&amp;lt;/strong&amp;gt;&amp;lt;/p&amp;gt; &amp;lt;p&amp;gt;Our client is a leading global healthcare organization, driving innovation in pharmaceuticals, biotechnology, and patient-centric solutions.&amp;lt;/p&amp;gt; &amp;lt;p&amp;gt;We develop advanced data and analytics solutions that help global </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Senior Business/System Analyst</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://careers.n-ix.com/jobs/4787051101?gh_jid=4787051101</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;Our client is a leading financial institution focused on digital innovation and customer-centric solutions. You will join a cross-functional Agile squad working on the development of a new, cutting-edge banking product aimed at redefining the digital experience for millions of users. The te</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4660259101</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;&amp;lt;span data-contrast=&amp;quot;auto&amp;quot;&amp;gt;Join us at Playtika (NASDAQ: PLTK), where we&amp;#39;re driven by the belief life needs play. We’re on a mission to deliver infinite ways to play using cutting-edge technologies like AI and machine learning to</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Games R&amp;D - R&amp;D Team Lead</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4880515101</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;&amp;lt;span data-contrast=&amp;quot;auto&amp;quot;&amp;gt;Join us at Playtika (NASDAQ: PLTK), where we&amp;#39;re driven by the belief life needs play. We’re on a mission to deliver infinite ways to play using cutting-edge technologies like AI and machine learning to</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing Strategy Manager - Maternity Leave Replacement </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Playtika</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.playtika.com/position/?gh_jid=4860542101</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;&amp;lt;span data-contrast=&amp;quot;auto&amp;quot;&amp;gt;Join us at Playtika (NASDAQ: PLTK), where we&amp;#39;re driven by the belief life needs play. We’re on a mission to deliver infinite ways to play using cutting-edge technologies like AI and machine learning to</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Marketing Data Analyst (part-time) в Dripify, віддалено</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/dripify/vacancies/363431/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a Marketing Data Analyst who will build Dripify’s marketing attribution and reporting. You will be the architect of how we understand marketing performance commercially: which channels drive revenue, which content converts to paid customers, and where our acquisition spend is a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Head of Analytics в TrueLabel, віддалено</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/truelabel/vacancies/352602/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>&lt;h3&gt;🎯 Role Overview&lt;strong&gt;&lt;/strong&gt;&lt;/h3&gt;&lt;p&gt;This is a &lt;strong&gt;senior business-facing role&lt;/strong&gt; for someone who can look beyond dashboards and understand what the numbers mean for strategy, risk, and growth.&lt;/p&gt;&lt;p&gt;We are an iGaming B2B platform operating on a revshare model. Our revenue is direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Старший(а) фахівець(чиня) з веб-аналітики та ефективності digital-платформ в Starlight Media, $1200–1700, віддалено</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/starlightmedia/vacancies/363423/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Starlight Media&lt;/strong&gt; — одна з найбільших медіагруп у Східній Європі, виробник та дистриб’ютор відеоконтенту, улюблених програм і серіалів мільйонів українців, якість та актуальність яких забезпечує нам лідерство. Понад половину українського ТБ-продукту, який ви бачите на екранах телев</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Медіа-аналітик/-киня в Національна суспільна телерадіокомпанія України, Київ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/natsionalna-suspilna-teleradiokompaniya-ukrajini/vacancies/363305/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Суспільне Мовлення&lt;/b&gt; — незалежна медіакомпанія України, яка об’єднує телевізійне, радійне та цифрове мовлення. Ми захищаємо свободи в Україні та надаємо суспільству достовірну і збалансовану інформацію. Завдяки широкій мережі каналів, радіостанцій і диджитал-платформ, Суспільне пропонує інфо</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Junior Cyber Security Analyst L1 в A4362, $500–1200, Одеса</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/a4362/vacancies/353759/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;В пошуку Junior Cyber Security Analyst (L1 SOC) для приєднання до нашої команди кібербезпеки.&lt;/p&gt;&lt;p&gt;Ви будете першою лінією захисту в Security Operations Center (SOC) та відповідатимете за безперервний моніторинг подій інформаційної безпеки, своєчасне виявлення потенційних загроз і первинну оброб</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IT Business Analyst (AI &amp;amp; Automation) — Helpware в Unicsoft, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/unicsoft/vacancies/363294/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Helpware is a global technology-driven company providing Customer Experience and Operational Support services across multiple regions.&lt;/p&gt;&lt;p&gt;Our Technology Team is growing, and we are looking for an IT Business Analyst (AI &amp;amp; Automation) to help bridge the gap between business stakeholders, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>QA Lead — Analyst (Complex ERP Systems) в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363280/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>&lt;h3&gt;About the Role&lt;/h3&gt;&lt;p&gt;We are looking for an experienced &lt;strong&gt;QA Lead — Analyst&lt;/strong&gt; to drive quality assurance and business quality analysis for complex ERP and enterprise financial systems. This role is ideal for a senior QA professional who combines strong testing leadership with analyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Business Analyst в Mticket, віддалено</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mticket/vacancies/358242/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a strong &lt;strong&gt;Senior Business Analyst / System Analyst&lt;/strong&gt; who can structure complex business processes, translate operational and product needs into clear requirements for the development team, and act as a key link between business, product, and engineering.&lt;/p&gt;&lt;p&gt;Thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Product Web Analyst | Edlight в Boosta, віддалено</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/boosta/vacancies/363254/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Привіт! &lt;br /&gt;Ми, Boosta — холдингова ІТ-компанія, яка створює, розвиває та інвестує в digital-бізнеси з глобальним потенціалом. Сьогодні з нами співпрацюють понад 700 фахівців з різних куточків світу, а нашими продуктами та сервісами користуються мільйони юзерів. &lt;/p&gt;&lt;p&gt;Наразі ми в пошуку &lt;b&gt;Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sales Intelligence Analyst в SQUAD, Київ, Львів, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/squad/vacancies/363230/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>&lt;h4&gt; Team Summary &lt;/h4&gt;  &lt;p&gt;The Business Development team is a three-member group focused on identifying, developing, and closing high-value business opportunities. Operating at the forefront of new market opportunities, we collaborate closely with Brand &amp;amp; Marketing, Engineering, and Executive L</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Threat Intelligence Analyst в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363200/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a Threat Intelligence Analyst to join our cybersecurity team and strengthen the company’s proactive defense capabilities.&lt;/p&gt;&lt;p&gt;This role combines cyber threat intelligence, proactive investigations, and risk-oriented analysis. We are looking for a specialist who can identify e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Business Analyst (Defense domain) в Ralabs, віддалено</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ralabs/vacancies/363197/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are seeking a talented &lt;strong&gt;Business Analyst&lt;/strong&gt; to join our dynamic team.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What is this project about?&lt;/strong&gt; &lt;br /&gt;An AI-powered analytics platform built for the defense domain. It ingests and analyzes data from multiple sources, automatically surfacing key findings an</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Head of Big Data Products в Vodafone Україна, Київ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/vodafone-ukraine/vacancies/356477/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Vodafone Україна&lt;/strong&gt; — лідер у сфері телекомунікацій та технологій, що активно впроваджує інновації в усіх напрямках діяльності. Ми об’єднуємо високі стандарти сервісу з найсучаснішими технологіями, такими як Cloud Services, Big Data, IoT та Smart City, щоб забезпечити наших клієнтів</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Head of Data Analytics в Міністерство оборони України, Київ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mod-of-ukraine/vacancies/346866/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>&lt;h3&gt;Про роль&lt;/h3&gt;&lt;p&gt;Ми шукаємо Head of Data Analytics, який/яка допоможе перетворювати дані на рішення.&lt;br /&gt;Це роль на перетині бізнесу, аналітики та продуктового мислення: від формування запиту до запуску аналітичного рішення та оцінки його реального впливу.&lt;/p&gt;&lt;p&gt;Ви будете координувати роботу ана</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Head of Data Analytics &amp;amp; Strategy в ROZETKA, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/356052/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Найпопулярнішому інтернет-магазину &lt;/strong&gt;&lt;a href="http://rozetka.ua/" target="_blank"&gt;&lt;strong&gt;Rozetka.ua&lt;/strong&gt;&lt;/a&gt;&lt;strong&gt; потрібен «Head of Data Analytics &amp;amp; Strategy».&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ROZETKA &lt;/strong&gt;— найбільший онлайн-ритейлер та один із найтехнологічніших e-commerce-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Head of Data Office в JSC Universal Bank, Київ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/universal-bank/vacancies/360184/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Universal Bank&lt;/b&gt; є сучасним українським банком зі стабільною репутацією протягом 30 років. Наш банк відомий завдяки успішному інноваційному проєкту &lt;b&gt;monobank&lt;/b&gt;, спільному роздрібному продукту Universal Bank у співпраці з IT-компанією Fintech Band, яким активно користуються вже понад 10 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Head of Analytics в UPG, віддалено</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/upg/vacancies/363048/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Команда UPG шукає амбітного та стратегічно мислячого лідера на позицію Director of Analytics, який має глибоку експертизу в індустрії Retail / E-commerce та практичний досвід впровадження технологій штучного інтелекту (AI) та машинного навчання (ML). Ця роль для тих, хто вміє перетворювати великі</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Head of Analytics в M32, віддалено</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/m32/vacancies/357782/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;М32 &lt;/b&gt;— це маркетингова компанія, яка займається розробкою та створенням соціальних платформ, performance-маркетингом та ІТ-рішеннями для соціальних мереж. Наша місія та спеціалізація — відкрити нові можливості соціальних взаємодій у цифровій мережі і забезпечення послуг повного циклу для кл</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Старший аналітик / Head of Commercial Analytics/Керівник напряму комерційної аналітики/бронювання/FMCG в GOLDEN STAFF, $1600–2000, Київ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/golden-staff/vacancies/361550/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Golden Staff шукає для партнера Старшого аналітика /Керівник напряму комерційної аналітики&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Наш партнер — велика українська виробнича компанія у сфері FMCG (харчова промисловість) зі штатом понад 1000 співробітників. Компанія активно трансформує бізнес-модель, посилює напрям</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Finance Analyst in Global BI Team (#1123) в ZONE3000, віддалено</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zone3000/vacancies/349277/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Location: Remote&lt;/b&gt;&lt;/p&gt;&lt;p&gt;&lt;b&gt;Your expertise:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience with financial KPIs, including profit and loss (P&amp;amp;L) statements&lt;/li&gt;&lt;li&gt;Experience in forecasting, performing what-if analyses, or building statistical models&lt;/li&gt;&lt;li&gt;At least 3 years of experience in analytics or a re</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst в Благодійна Організація Благодійний Фонд "Спільнота Стерненка", Київ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/blagodiina-organizatsiya-blagodiinii-fond-spilnota-sternenka/vacancies/358820/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Вітаємо, друже! &lt;br /&gt;Благодійний Фонд «Спільнота Стерненка» є найбільшим недержавним постачальником FPV-дронів до війська. Станом на травень 2026 року ми закупили та передали до Сил Оборони більше ніж 275000 дронів і на цьому не зупиняємося.&lt;/p&gt;&lt;p&gt;Якщо ти розумієш важливість того, що ми робимо, </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Middle/Senior Data Analyst в BOOSTERS - Product Team, віддалено</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/boosters-product-team/vacancies/352931/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://boosters.team/" target="_blank"&gt;&lt;strong&gt;Boosters&lt;/strong&gt;&lt;/a&gt; — це українська продуктова компанія. Ми створюємо глобальні продукти в сферах EdTech, Productivity та Wellness, які несуть цінність для&lt;strong&gt; 55 мільйонів людей&lt;/strong&gt;. Для нас важливо будувати продукти з довготрив</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Lead Product/Data Analyst в Association of Ukrainian Defense Manufacturers, $1500–2000, Київ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/association-of-ukrainian-defense-manufacturers/vacancies/362306/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми розробляємо та вдосконалюємо складні апаратні рішення (Hardware) та системи зв’язку для безпеки України. Шукаємо &lt;b&gt;Lead Analyst&lt;/b&gt;, який очолить команду з 5 спеціалістів, вибудує з нуля систему збору даних з реальних умов експлуатації та допоможе модернізувати нашу продуктову лінійку.&lt;/p&gt;&lt;h3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Data Analyst (Performance Marketing Team) в King Group, Київ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/king-group/vacancies/362284/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Вітаємо в &lt;strong&gt;King Group&lt;/strong&gt; — місці, де зустрічаються найкращі люди з IT- та гемблінг-індустрії, аби створювати успішні продукти. До складу King Group входить низка проектів у сфері iGaming на ринках України та Tier-1, ми інвестуємо у венчурні стартапи, перспективні ідеї та людей.&lt;br /&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Data Analytics Lead в Uklon, Київ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/uklon/vacancies/351376/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>&lt;blockquote&gt;Uklon — продуктова IT-компанія, що розробляє провідний райд-хейлінг сервіс. Щодня потужна команда Uklon прокачує одну з найбільших інфраструктур на ринку України та за її межами, забезпечуючи взаємодію драйверів та райдерів.&lt;/blockquote&gt;  &lt;p&gt;Ми створюємо highload продукт, за яким ховають</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/828570-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a Quantitative Analyst to become the mathematical backbone of our Trading Core and Risk Tech squads. In a high-frequency trading environment processing billions in volume, success is defined by precision.&amp;nbsp;&lt;/p&gt;&lt;p&gt;In this role, you will design, backtest, and optimize the cor</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mapping and Transition Tables Analyst</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827449-mapping-and-transition-tables-analyst/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Офіс ефективного регулювання &lt;strong&gt;BRDO&lt;/strong&gt; - один із ключових незалежних експертно-аналітичних центрів України. Ми працюємо над проєктуванням сучасних регуляторних та цифрових рішень для держави.&amp;nbsp;&lt;br /&gt;&lt;br /&gt;Шукаємо &lt;strong&gt;Аналітик таблиць відповідності та переходу (Mapping &amp;amp; Tr</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Data Engineer/Analyst (GCP)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827044-data-engineer-analyst-gcp/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Cloudfresh ⛅️ is a Global Google Cloud Premier Partner, Zendesk Premier Partner, Asana Solutions Partner, GitLab Select Partner, Hubspot Platinum Partner, Okta Activate Partner, and Microsoft Partner.&lt;br /&gt;&lt;br /&gt;Since 2017, we’ve been specializing in the implementation, migration, integration, au</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/828573-quantitative-analyst/</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a &lt;strong&gt;Quantitative Analyst&lt;/strong&gt; to become the mathematical backbone of our Trading Core and Risk Tech squads. In a high-frequency trading environment processing billions in volume, success is defined by precision.&amp;nbsp;&lt;/p&gt;&lt;p&gt;In this role, you will design, backtest, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HR Analyst</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833704-hr-analyst/</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Шукаємо HR Analyst, який відповідатиме за побудову системної HR-аналітики, розвиток Power BI dashboards, формування HR Metrics Book, регулярну управлінську звітність, risk map, ad hoc analytics та підготовку аналітичних висновків для бізнесу.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Основні обов’язки&lt;/strong&gt;&lt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833696-ice-hockey-analyst/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Our client is leading supplier of sports analytics to its clients. Using cutting edge Computer Vision and AI/ML technologies, the company provides outstanding real-time sports performance analysis. As an analyst you will be responsible for providing quality statistics for ice hockey games using c</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик / Фінансист</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833671-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми шукаємо системного спеціаліста, який візьме на себе контроль фінансових потоків, звітність та аналітику. Якщо ви маєте здоровий «бухгалтерський скептицизм», вмієте працювати з цифрами та хочете розвиватися у сфері FinTech/high-risk — будемо раді бачити вас у команді.&lt;/p&gt;&lt;p&gt;Основні обов'язки:&lt;/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик (міжнародні ринки капіталу, навчання)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833670-finansovii-analitik-mizhnarodni-rinki-kapital/</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми шукаємо молодшого фінансового аналітика, який готовий перетворити вміння працювати з цифрами на результат.&lt;/p&gt;&lt;p&gt;Навіть якщо у вас немає досвіду роботи з біржами – ми надаємо повне прикладне навчання аналізу ринків.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Формат роботи:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Виключн</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Risk Operations Analyst/IGaming/Antifraud</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833657-risk-operations-analyst-igaming-antifraud/</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are an iGaming company with over 3 years of experience and a team of 1,300+ professionals. Our portfolio includes 10+ successful projects operating across Tier 1–3 markets. We value expertise, innovation, and efficiency, creating an environment where talented professionals can grow and make an</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833663-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Inception-1&amp;nbsp;&lt;/strong&gt;is a&amp;nbsp;fast-growing product company. We&amp;nbsp;create AI-driven products that help people feel more connected and less alone. Our mission is&amp;nbsp;to&amp;nbsp;build meaningful digital experiences that blend technology with empathy&amp;nbsp;— and to&amp;nbsp;prove that&amp;nbsp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BI Analyst / Data Engineer</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833549-bi-analyst-data-engineer/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Position Overview&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are looking for a BI Analyst / Data Engineer to join our team and drive data-informed decision-making across the organization. In this role, you will work closely with business stakeholders, product teams, and leadership to analyze data, develop reporti</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Head of Data</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833000-head-of-data/</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Наша команда UPG активно трансформує &amp;nbsp;бізнес-процеси та створює сучасну екосистему роботи з даними. Для реалізації нашої AI-стратегії ми шукаємо фундаментального технічного лідера, який побудує сучасну, високотехнологічну інфраструктуру, що стане надійним фундаментом для навчання та роботи м</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bonus Marketing Manager (Trainee) SoftSvit — продуктова IT компанія, яка створює та просуває власні веб-проєкти. Шукаємо</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>@Space_Job</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Telegram/Space_Job</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://t.me/Space_Job/2977</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bonus Marketing Manager (Trainee) SoftSvit — продуктова IT компанія, яка створює та просуває власні веб-проєкти. Шукаємо Bonus Marketing Manager (Trainee): якщо ти на старті кар'єри й хочеш рости поруч із досвідченими спеціалістами — ця позиція для тебе. Ти наш кандидат, якщо: Володієш Google Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Workday Financials Analyst Consultant (Global Delivery Center)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Collaborative Solutions</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/collaborative-solutions-workday-financials-analyst-consultant-global-delivery-center</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>&lt;img src="https://we-work-remotely.imgix.net/logos/0171/5633/logo.gif?ixlib=rails-4.0.0&amp;amp;w=50&amp;amp;h=50&amp;amp;dpr=2&amp;amp;fit=fill&amp;amp;auto=compress" /&gt;  &lt;p&gt;   &lt;strong&gt;Headquarters:&lt;/strong&gt; PHL - Manila - Remote     &lt;br /&gt;&lt;strong&gt;URL:&lt;/strong&gt; &lt;a href="http://collaborativesolutions.com"&gt;http://collab</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Business &amp; CRM Analyst | Remote</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sonova International</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/sonova-international-business-crm-analyst-remote-1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>&lt;img src="https://we-work-remotely.imgix.net/logos/0171/5612/logo.gif?ixlib=rails-4.0.0&amp;amp;w=50&amp;amp;h=50&amp;amp;dpr=2&amp;amp;fit=fill&amp;amp;auto=compress" /&gt;  &lt;p&gt;   &lt;strong&gt;Headquarters:&lt;/strong&gt; Mexico     &lt;br /&gt;&lt;strong&gt;URL:&lt;/strong&gt; &lt;a href="http://sonova.com"&gt;http://sonova.com&lt;/a&gt; &lt;/p&gt;  &lt;div class="exte</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Data Analyst/ Curam</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AHU Technologies</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/ahu-technologies-data-analyst-curam</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;   &lt;strong&gt;Headquarters:&lt;/strong&gt; Fully Remote - US     &lt;br /&gt;&lt;strong&gt;URL:&lt;/strong&gt; &lt;a href="http://ahutech.com"&gt;http://ahutech.com&lt;/a&gt; &lt;/p&gt;  &lt;div class="job-description-container"&gt; &lt;div class="trix-content"&gt; &lt;div&gt;&lt;strong&gt;Job Description:&amp;nbsp;&lt;/strong&gt;&lt;/div&gt;&lt;div&gt;&lt;strong&gt;Short Description:&lt;/stron</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (w/m/d) für SaaS und On-Premises Lösungen</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Septeo CNEE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/septeo-cnee-product-marketing-manager-w-m-d-fur-saas-und-on-premises-losungen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>&lt;img src="https://we-work-remotely.imgix.net/logos/0171/5531/logo.gif?ixlib=rails-4.0.0&amp;amp;w=50&amp;amp;h=50&amp;amp;dpr=2&amp;amp;fit=fill&amp;amp;auto=compress" /&gt;  &lt;p&gt;   &lt;strong&gt;Headquarters:&lt;/strong&gt; Karlsruhe, DE, Lauf a. d. Pegnitz, DE, Nordwalde, DE, Remote, Germany     &lt;br /&gt;&lt;strong&gt;URL:&lt;/strong&gt; &lt;a href="</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Elite Software Automation</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/elite-software-automation-business-analyst-2</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>&lt;img src="https://we-work-remotely.imgix.net/logos/0083/7653/logo.gif?ixlib=rails-4.0.0&amp;amp;w=50&amp;amp;h=50&amp;amp;dpr=2&amp;amp;fit=fill&amp;amp;auto=compress" /&gt;  &lt;p&gt;   &lt;strong&gt;Headquarters:&lt;/strong&gt; Virtual     &lt;br /&gt;&lt;strong&gt;URL:&lt;/strong&gt; &lt;a href="https://jobs.elitesoftwareautomation.com/"&gt;https://jobs.elites</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F513"/>
+  <dimension ref="A1:F514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16818,6 +16818,38 @@
       <c r="F513" t="inlineStr">
         <is>
           <t>2026-06-24 22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>DXC_8eb68b759a82</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Service Request Management &amp; Process Analyst</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/MEX---DIF---MEXICO-CITY/Service-Request-Management---Process-Analyst_51583844-1</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04</t>
         </is>
       </c>
     </row>
@@ -16832,7 +16864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F513"/>
+  <dimension ref="A1:F514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -33153,7 +33185,38 @@
           <t>https://weworkremotely.com/remote-jobs/ahu-technologies-senior-technical-business-analyst-atlanta-ga</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:04</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Service Request Management &amp; Process Analyst</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/MEX---DIF---MEXICO-CITY/Service-Request-Management---Process-Analyst_51583844-1</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>MEX - DIF - MEXICO CITY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F514"/>
+  <dimension ref="A1:F515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16850,6 +16850,38 @@
       <c r="F514" t="inlineStr">
         <is>
           <t>2026-06-25 00:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>luxoft_ab733bfeebff</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Murex FO Business Analyst</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/job/murex-fo-business-analyst-25405</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:50</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F514"/>
+  <dimension ref="A1:F515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -33218,6 +33250,38 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:50</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Murex FO Business Analyst</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/job/murex-fo-business-analyst-25405</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Murex FO | Kuala Lumpur | Malaysia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F515"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16882,6 +16882,134 @@
       <c r="F515" t="inlineStr">
         <is>
           <t>2026-06-25 02:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833792-middle-business-process-analyst-u-produktovu-/</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Middle Business-process analyst у продуктову компанію</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833792-middle-business-process-analyst-u-produktovu-/</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833795-data-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Data Marketing Analyst</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833795-data-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833771-mobile-app-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Mobile App Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833771-mobile-app-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/769542-creatio-system-analyst/</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Creatio System analyst</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/769542-creatio-system-analyst/</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
         </is>
       </c>
     </row>
@@ -16896,7 +17024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F515"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -33282,6 +33410,134 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Middle Business-process analyst у продуктову компанію</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833792-middle-business-process-analyst-u-produktovu-/</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Компанія з виробничої сфери знаходиться в пошуку Business-process analyst.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Спеціаліст буде відповідати за:&lt;/p&gt;&lt;p&gt;- Аналіз поточних бізнес процесів&lt;/p&gt;&lt;p&gt;-&amp;nbsp;Реінжинірінг та оптимізація процесів&lt;/p&gt;&lt;p&gt;-&amp;nbsp;Побудова нових процесів&lt;/p&gt;&lt;p&gt;-&amp;nbsp;Формування процесної документац</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Data Marketing Analyst</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833795-data-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;At A-Players, we are building a new AI product in the mental health and mindfulness space - and we are looking for a&amp;nbsp;&lt;strong&gt;Data &amp;amp; Marketing Analyst&lt;/strong&gt; who will own the analytics layer from day one.&lt;/p&gt;&lt;p&gt;We are not building analytics after the fact. We are building it before the </t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Mobile App Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833771-mobile-app-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;The Role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We're looking for a Junior/Mid-level Mobile App Growth Marketer to drive awareness and gain traction for the Delurk app in Ukraine. You'll own how Delurk gets discovered — finding the right audiences, getting the app in front of them, and turning early curiosity in</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Creatio System analyst</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/769542-creatio-system-analyst/</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;🚀 Про нас&lt;/p&gt;&lt;p&gt;SYNTECH.digital&amp;nbsp;— команда, яка перетворює хаос процесів на&amp;nbsp;системність. Ми&amp;nbsp;створюємо &lt;strong&gt;продуктові рішення для виробництва, фінансів, рітейлу та&amp;nbsp;сервісів&lt;/strong&gt;, використовуючи &lt;strong&gt;no-code платформу Creatio&lt;/strong&gt;. Ми&amp;nbsp;працюємо як&amp;nbsp;стартап:</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F519"/>
+  <dimension ref="A1:F533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17010,6 +17010,454 @@
       <c r="F519" t="inlineStr">
         <is>
           <t>2026-06-25 06:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>globallogic_d3c79c8299d7</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298682/</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>luxoft_181ce8915e5c</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Senior System Analyst</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/job/senior-system-analyst-25430</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>tieto_e4979a8a2281</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Business Analyst, Tieto Banktech (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>https://careers.tieto.com/job/business-analyst-tieto-banktech-m-f-d-in-fornebu-norway-jid-1962</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/honeytech/vacancies/363524/?1782381916</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>BI Analyst в Honeytech, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/honeytech/vacancies/363524/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/honeytech/vacancies/363522/?1782381232</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Middle Marketing Analyst в Honeytech, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/honeytech/vacancies/363522/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nda-recruitment/vacancies/363488/?1782376132</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>HR Analytics Manager в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363488/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/gismart_com/vacancies/363482/?1782375779</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Billing Analyst в Gismart, віддалено</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/gismart_com/vacancies/363482/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/353985/?1782372662</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик IT Enterprise в ROZETKA, віддалено</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/353985/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/kitsoft/vacancies/363469/?1782372211</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Business Analyst в Kitsoft, віддалено</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/kitsoft/vacancies/363469/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/822616-pr-manager-infuencer-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>PR Manager / Infuencer Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/822616-pr-manager-infuencer-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833864-middle-senior-data-analyst/</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Middle+/Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833864-middle-senior-data-analyst/</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/802668-influencer-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager for Tier-1</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/802668-influencer-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/754163-affiliate-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Affiliate Marketing Manager for Tier-1</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/754163-affiliate-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833852-analitik-marketing-department/</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Аналітик (Marketing Department)</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833852-analitik-marketing-department/</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F519"/>
+  <dimension ref="A1:F533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -33538,6 +33986,449 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298682/</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Senior System Analyst</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/job/senior-system-analyst-25430</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Functional/System Analysis | Kuala Lumpur | Malaysia</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Business Analyst, Tieto Banktech (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://careers.tieto.com/job/business-analyst-tieto-banktech-m-f-d-in-fornebu-norway-jid-1962</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>BI Analyst в Honeytech, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/honeytech/vacancies/363524/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>&lt;blockquote&gt;&lt;p&gt;Ти працюєш пліч-о-пліч з досвідченими аналітиками, які готові ділитися знаннями та допомагати у твоєму професійному розвитку, освоюєш нові навички, займаєшся цікавими задачами, що прокачують твої скіли та допомагають рости професійно — звучить круто, чи не так? Все це можливо з нами!&lt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Middle Marketing Analyst в Honeytech, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/honeytech/vacancies/363522/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>&lt;blockquote&gt;&lt;p&gt;Шукаємо Marketing Data Analyst, який не просто зводить дані — а бачить у них можливості для росту 🚀&lt;/p&gt;&lt;p&gt;Якщо тебе драйвить знаходити точки масштабування, будувати гнучку аналітичну інфраструктуру та впливати на маркетинг через цифри — це саме той виклик, якого ти чекав!&lt;/p&gt;&lt;/blockqu</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>HR Analytics Manager в NDA Recruitment, Київ</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nda-recruitment/vacancies/363488/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Команда нашого клієнта розширює команду та шукає HR Analytics Manager, який допоможе перетворювати дані на рішення та стане ключовим партнером для HR-команди та бізнесу. &lt;/p&gt;&lt;p&gt;У цій ролі ви будете відповідати за розвиток HR-аналітики, побудову системи звітності, контроль якості даних та формуван</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Billing Analyst в Gismart, віддалено</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/gismart_com/vacancies/363482/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;About us:&lt;/b&gt; &lt;br /&gt;Gismart is a value-driven mobile app developer with a strong presence in the Health &amp;amp; Wellness, Utilities, and Music app markets. We have achieved a significant milestone of over 1 billion downloads worldwide, taking a step toward our mission of cultivating the well-bei</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик IT Enterprise в ROZETKA, віддалено</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/rozetka-ua-internet-supermarket/vacancies/353985/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Найпопулярнішому інтернет-магазину &lt;a href="http://rozetka.ua/" target="_blank"&gt;Rozetka.ua&lt;/a&gt; потрібен &lt;b&gt;«Бізнес-аналітик»&lt;/b&gt;&lt;/p&gt;&lt;p&gt;&lt;b&gt;ROZETKA &lt;/b&gt;— найбільший онлайн-ритейлер та один із найтехнологічніших e-commerce-проектів в Україні. Наша місія — бути універсальним помічником з вибору будь-</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Business Analyst в Kitsoft, віддалено</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/kitsoft/vacancies/363469/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Kitsoft — українська GovTech-компанія, яка допомагає створювати цифрові держави нового покоління. &lt;/strong&gt;Ми понад 11 років розробляємо та впроваджуємо цифрові сервіси для мільйонів людей, змінюючи те, як громадяни взаємодіють із державою — швидко, зручно та прозоро.&lt;/p&gt;&lt;p&gt;Швидше за все,</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>PR Manager / Infuencer Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/822616-pr-manager-infuencer-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gazer – це&amp;nbsp;система, яка виключає злочин.&lt;/p&gt;&lt;p&gt;Ми&amp;nbsp;об'єднуємо людей та&amp;nbsp;технології у&amp;nbsp;систему колективної безпеки, де&amp;nbsp;кожен відповідає за&amp;nbsp;всіх. Наші пристрої — це&amp;nbsp;не&amp;nbsp;просто техніка, а&amp;nbsp;частина нової реальності,&amp;nbsp;же кожен автомобіль це&amp;nbsp;частина мере</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Middle+/Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833864-middle-senior-data-analyst/</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Компанія з виробничої сфери знаходиться в пошуку Data Analyst.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Спеціаліст буде відповідати за:&lt;br /&gt;- Збір, перевірку та підготовку даних із різних джерел&lt;br /&gt;- Розробку та підтримку дашбордів і звітності в Tableau&lt;br /&gt;- Аналіз бізнес-показників і підготовку рекомендацій для </t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager for Tier-1</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/802668-influencer-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;King Group&lt;/strong&gt; — це сучасна компанія з інноваційним підходом до просування брендів.&amp;nbsp;&lt;br /&gt;Ми працюємо у сфері iGaming та маємо&amp;nbsp;&lt;strong&gt;три&amp;nbsp;&lt;/strong&gt;успішні українські бренди онлайн-казино, а також власні партнерські мережі. Активно працюємо як з локальними ринками, так</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Affiliate Marketing Manager for Tier-1</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/754163-affiliate-marketing-manager-for-tier-1/</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;King Group&lt;/strong&gt; — це сучасна компанія з інноваційним підходом до просування брендів.&amp;nbsp;&lt;br /&gt;Ми працюємо у сфері iGaming та маємо&amp;nbsp;&lt;strong&gt;три&amp;nbsp;&lt;/strong&gt;успішні українські бренди онлайн-казино, а також власні партнерські мережі. Активно працюємо як з локальними ринками, так</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Аналітик (Marketing Department)</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833852-analitik-marketing-department/</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Вимоги&lt;/strong&gt;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;досвід роботи з маркетинговою аналітикою або аналітикою даних буде перевагою&lt;/li&gt;&lt;li&gt;розуміння основ маркетингових метрик&lt;/li&gt;&lt;li&gt;базові знання SQL або аналітичних інструментів — плюс&lt;/li&gt;&lt;li&gt;аналітичне мислення, уважність до деталей, системність&lt;/li&gt;&lt;li&gt;Готовн</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F533"/>
+  <dimension ref="A1:F549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17458,6 +17458,518 @@
       <c r="F533" t="inlineStr">
         <is>
           <t>2026-06-25 10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>epam_9713f0d86f1f</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Business Analyst (Insurance)</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/blt78pnwlr43osqmirg</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>epam_6a46095ada2e</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Senior BI Business Analyst</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/bltdjp3iaxfyjlhcxeg</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>globallogic_1ca10f489033</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Senior/Lead Business Analyst for Energy program</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/senior-lead-business-analyst-for-energy-program-irc298700/</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ciklum_cb953f6ca592</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>https://explore-jobs.ciklum.com/en/sites/ciklum-career/job/3483</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>novadigital_1b23d436a27d</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик (кадровий облік, заробітна плата)</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363531/?lang=en</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/ciklum/vacancies/363570/?1782392316</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (3483) в Ciklum, Київ, Львів, віддалено</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ciklum/vacancies/363570/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/pivdenny/vacancies/363548/?1782387904</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>IT Business Analyst в Bank Pivdenny, Київ, Одеса, віддалено</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/pivdenny/vacancies/363548/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nova-digital/vacancies/363531/?1782384631</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик (кадровий облік, заробітна плата) в Nova Digital, віддалено</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363531/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/drumncode/vacancies/354477/?1782384015</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в Drum'N'Code, віддалено</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/drumncode/vacancies/354477/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833939-senior-soc-analyst-with-microsoft-security-st/</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Senior SOC Analyst with Microsoft Security Stack</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833939-senior-soc-analyst-with-microsoft-security-st/</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833934-product-marketing-manager-partnership-project/</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager - Partnership Project</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833934-product-marketing-manager-partnership-project/</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833927-ice-hockey-analyst-irc298682/</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst (IRC298682)</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833927-ice-hockey-analyst-irc298682/</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/824651-affiliate-analyst-junior/</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Affiliate Analyst Junior</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/824651-affiliate-analyst-junior/</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/831252-senior-business-analyst/</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831252-senior-business-analyst/</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/827317-product-marketing-manager-technical-content-m/</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager/Technical Content Manager</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827317-product-marketing-manager-technical-content-m/</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/831790-performance-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Performance Marketing Analyst</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831790-performance-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
         </is>
       </c>
     </row>
@@ -17472,7 +17984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F533"/>
+  <dimension ref="A1:F549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -34429,6 +34941,518 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Business Analyst (Insurance)</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/blt78pnwlr43osqmirg</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Senior BI Business Analyst</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/bltdjp3iaxfyjlhcxeg</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Senior/Lead Business Analyst for Energy program</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/senior-lead-business-analyst-for-energy-program-irc298700/</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://explore-jobs.ciklum.com/en/sites/ciklum-career/job/3483</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>UA | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик (кадровий облік, заробітна плата)</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363531/?lang=en</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (3483) в Ciklum, Київ, Львів, віддалено</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ciklum/vacancies/363570/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Ciklum&lt;/strong&gt; is looking for a &lt;strong&gt;Senior Business Analyst&lt;/strong&gt; to join our team full-time in Ukraine.&lt;/p&gt;  &lt;p&gt;We are a custom product engineering company that supports both multinational organizations and scaling startups to solve their most complex business challenges. With a </t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>IT Business Analyst в Bank Pivdenny, Київ, Одеса, віддалено</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/pivdenny/vacancies/363548/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Банк «Південний» &lt;/strong&gt;— один із лідерів фінансового ринку України, який займає третє місце у групі українських банків із приватним капіталом за розміром активів. Вже 32 роки «Південний» є надійним фінансовим партнером для приватних клієнтів, малого, середнього і корпоративного бізнесу</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик (кадровий облік, заробітна плата) в Nova Digital, віддалено</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363531/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Не просто код, а твій вплив на мільйони українців&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Nova Digital — це технологічне серце екосистеми NOVA, де твій код стає частиною щоденного життя цілої країни.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Про масштаб наших сервісів:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;• 50+ млн запитів щодня проходять через наші системи&lt;br /</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в Drum'N'Code, віддалено</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/drumncode/vacancies/354477/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Drum’N’Code is a Ukrainian IT company with over &lt;b&gt;10 years of experience&lt;/b&gt; in building reliable, creative, and well-tested digital solutions.&lt;br /&gt;We work with clients worldwide, helping them turn ideas into real, impactful products.&lt;/p&gt;&lt;p&gt;We’re currently looking for a Project Manager with str</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Senior SOC Analyst with Microsoft Security Stack</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833939-senior-soc-analyst-with-microsoft-security-st/</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Project overview&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;This project focuses on building and enhancing a mature cyber defense capability that combines advanced incident response with security engineering and automation. The goal is to improve detection accuracy, accelerate response times, and strengthen protecti</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager - Partnership Project</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833934-product-marketing-manager-partnership-project/</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми — &lt;strong&gt;NetSolid Investments&lt;/strong&gt; — інвестиційний фонд, заснований в Україні, з основним фокусом на SMART-інвестиції. Ми інвестуємо не лише фінанси, а й експертизу у сферах digital marketing, IT та traffic-проєктів, допомагаючи молодим компаніям ставати лідерами у своїй ніші.&lt;/p&gt;&lt;p&gt;&lt;br /</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst (IRC298682)</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833927-ice-hockey-analyst-irc298682/</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Job Description&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;- Confident PC user (Windows)&lt;br /&gt;- Basic English&lt;br /&gt;- Extensive internet research skills&lt;br /&gt;- Creative problem-solving and analysis skills&lt;br /&gt;- Team player with good interpersonal and solution-oriented attitude&lt;br /&gt;- Readiness to work i</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Affiliate Analyst Junior</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/824651-affiliate-analyst-junior/</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are currently looking for an Affiliate Analyst.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Responsibilities:&lt;/strong&gt;&lt;br /&gt;&amp;nbsp;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Analyze incoming and outgoing traffic: sources, offers, GEOs, devices, landing pages, CR/EPC/ROI.&lt;/li&gt;&lt;li&gt;Prepare daily/weekly/monthly performance reports.&lt;br /&gt;Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831252-senior-business-analyst/</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Senior Business Analyst&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We encourage you to apply if you are an agile, smart, proactive, and intellectually curious person who loves building complex systems while keeping them inherently simple.&lt;/p&gt;&lt;p&gt;You will work with our Busines</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager/Technical Content Manager</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827317-product-marketing-manager-technical-content-m/</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Meet the YozmaTech&lt;/strong&gt;&lt;br /&gt;&lt;br /&gt;YozmaTech isn’t just another tech company – we’re a global team of go-getters, innovators, and A-players helping startups and product companies scale smarter and faster.&lt;br /&gt;We build dedicated development teams across 10+ countries, creating strong,</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Performance Marketing Analyst</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831790-performance-marketing-analyst/</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Про нас:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ми - маркетингова компанія з 7-річним досвідом роботи на ринку.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;i&gt;Шукаємо не просто аналітика звітів, а людину, яка буде занурена в процес заливу трафіку, аналізуватиме дані та допомагатиме команді приймати рішення для зростання результатів і прибутку.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F549"/>
+  <dimension ref="A1:F550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17970,6 +17970,38 @@
       <c r="F549" t="inlineStr">
         <is>
           <t>2026-06-25 13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833971-b2b-marketing-manager-demand-partner-marketin/</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>B2B Marketing Manager / Demand  Partner Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833971-b2b-marketing-manager-demand-partner-marketin/</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:09</t>
         </is>
       </c>
     </row>
@@ -17984,7 +18016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F549"/>
+  <dimension ref="A1:F550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -35453,6 +35485,38 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:09</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>B2B Marketing Manager / Demand  Partner Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833971-b2b-marketing-manager-demand-partner-marketin/</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Ми виробляємо преміальні глемпінг-модулі та продаємо їх архітекторам,&amp;nbsp;готельним девелоперам та операторам glamping&amp;nbsp;по всій Європі.&amp;nbsp;Ціна угоди — від €80K до €500K+. Цикл продажу — 3-12 місяців. Нам потрібна людина, яка вміє будувати B2B-воронку та оркеструвати маркетингову д</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F550"/>
+  <dimension ref="A1:F552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18002,6 +18002,70 @@
       <c r="F550" t="inlineStr">
         <is>
           <t>2026-06-25 14:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ciklum_1b9f38268c50</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>https://explore-jobs.ciklum.com/en/sites/ciklum-career/job/3574</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833955-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833955-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F550"/>
+  <dimension ref="A1:F552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -35517,6 +35581,70 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://explore-jobs.ciklum.com/en/sites/ciklum-career/job/3574</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>CZ | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833955-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Reblum&amp;nbsp;&lt;/strong&gt;— компанія, яка розробляє власні AI-технології для обробки зображень. Наш основний продукт&amp;nbsp;— reblum.app, десктопний застосунок для професійних портретних фотографів та&amp;nbsp;ретушерів.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ми&amp;nbsp;шукаємо &lt;strong&gt;Marketing Manager&lt;/strong&gt;, який(а) </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F552"/>
+  <dimension ref="A1:F558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18066,6 +18066,198 @@
       <c r="F552" t="inlineStr">
         <is>
           <t>2026-06-25 14:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>epam_acf4beb13044</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Lead BI Business Analyst</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/bltr45j9xwohgletse7</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>globallogic_574e474a9e28</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298685/</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/at-oschadbank/vacancies/363600/?1782398374</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Інвестиційний аналітик (Департамент преміального банкінгу) в АТ "Ощадбанк", Київ</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/at-oschadbank/vacancies/363600/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/de-novo/vacancies/363612/?1782399981</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Бізнес аналітик (Middle) в De Novo, Київ</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/de-novo/vacancies/363612/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/823062-creative-marketing-manager-meta/</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Creative Marketing Manager(META)</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/823062-creative-marketing-manager-meta/</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/831249-senior-soc-analyst/</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Senior SOC Analyst</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831249-senior-soc-analyst/</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F552"/>
+  <dimension ref="A1:F558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -35645,6 +35837,198 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Lead BI Business Analyst</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/jobs/bltr45j9xwohgletse7</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298685/</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Інвестиційний аналітик (Департамент преміального банкінгу) в АТ "Ощадбанк", Київ</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/at-oschadbank/vacancies/363600/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;МІЙ БАНК — МОЯ ОПОРА.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Опора мільйонів українців, хто відтепер каже «МОЄ».&lt;/p&gt;&lt;p&gt;&lt;strong&gt;МОЇ ЛЮДИ. МОЯ СПРАВА. МОЯ СВОБОДА.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ОЩАДБАНК запрошує до команди Інвестиційного аналітика (Департамент преміального банкінгу)&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ця позиція підійде тим,</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Бізнес аналітик (Middle) в De Novo, Київ</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/de-novo/vacancies/363612/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Основні обов’язки&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Аналіз, реінжиніринг та автоматизація бізнес-процесів компанії.&lt;/li&gt;&lt;li&gt;Збір, аналіз і формалізація бізнес- та функціональних вимог від внутрішніх замовників і зацікавлених сторін.&lt;/li&gt;&lt;li&gt;Моделювання бізнес-процесів і опис цільових рішень у нотаціях BPMN/UML.&lt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Creative Marketing Manager(META)</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/823062-creative-marketing-manager-meta/</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Шукаємо людину, яка повністю володітиме креативним напрямком продукту для Paid Ads і для органічних каналів, відео і статика.&amp;nbsp;&lt;br /&gt;Не менеджер, який пересилає брифи. Не "начальник банерів". Людина з головою і руками: думає метриками, створює сама, а підрядників і команду використовує для ма</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Senior SOC Analyst</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831249-senior-soc-analyst/</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Position Name&lt;/strong&gt;: Senior SOC Analyst&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Reports to&lt;/strong&gt;: Team Lead, SOC&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location&lt;/strong&gt;: Remote, Philippines&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Role Overview&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Atlas Technica's mission is to shoulder IT management, user support, and cybersecurity </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F558"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18258,6 +18258,70 @@
       <c r="F558" t="inlineStr">
         <is>
           <t>2026-06-25 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/827381-product-analyst/</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827381-product-analyst/</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834002-senior-network-security-analyst/</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Senior Network Security Analyst</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834002-senior-network-security-analyst/</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:22</t>
         </is>
       </c>
     </row>
@@ -18272,7 +18336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F558"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -36029,6 +36093,70 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:22</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827381-product-analyst/</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Наш клієнт&amp;nbsp;— міжнародна маркетингова компанія, яка стрімко масштабується та&amp;nbsp;займає провідну позицію в&amp;nbsp;індустрії iGaming, з&amp;nbsp;особливою увагою до&amp;nbsp;ринку Азії.&lt;/p&gt;&lt;p&gt;Від глибоких досліджень ринку та&amp;nbsp;розробки стратегії до&amp;nbsp;результативних діджитал-кампаній і&amp;nbsp;смілив</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:22</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Senior Network Security Analyst</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834002-senior-network-security-analyst/</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми шукаємо &lt;strong&gt;Senior Network Security Analyst&lt;/strong&gt;, який допоможе оцінювати та посилювати рівень мережевої безпеки корпоративної інфраструктури компанії.&lt;br /&gt;&amp;nbsp;&lt;br /&gt;&amp;nbsp;Це роль для експерта, який вміє дивитися на мережу комплексно: від архітектури та маршрутизації до аналізу ризи</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18322,6 +18322,102 @@
       <c r="F560" t="inlineStr">
         <is>
           <t>2026-06-25 16:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>novadigital_868b4766ae32</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>MS Dynamics ERP ВС Business Analyst</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/353841/?lang=en</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nova-digital/vacancies/353841/?1782409316</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>MS Dynamics ERP ВС Business Analyst в Nova Digital, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/353841/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/809751-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/809751-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -36157,6 +36253,102 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>MS Dynamics ERP ВС Business Analyst</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/353841/?lang=en</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Kyiv, remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>MS Dynamics ERP ВС Business Analyst в Nova Digital, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/353841/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Не просто код, а твій вплив на мільйони українців&lt;/strong&gt; &lt;br /&gt;Nova Digital — це технологічне серце екосистеми NOVA, де твій код стає частиною щоденного життя цілої країни.&lt;br /&gt;&lt;br /&gt;&lt;strong&gt;Про масштаб наших сервісів:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;50+ млн запитів щодня проходять через наші сист</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/809751-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Ringostat&lt;/strong&gt; — українська AI-платформа для бізнесу, що надає інструменти телефонії, колтрекінгу та аналітики дзвінків. Наш успіх підтверджує довіра понад 2300 компаній, серед яких відомі бренди Peugeot, Mercedes-Benz, Jooble та OLX. Ми маємо широку партнерську мережу з більш ніж 250</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F563"/>
+  <dimension ref="A1:F566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18418,6 +18418,102 @@
       <c r="F563" t="inlineStr">
         <is>
           <t>2026-06-25 18:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>DXC_a8413be314b1</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Analyst III Infrastructure services</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/IND---KA---BANGALORE/Analyst-III-Infrastructure-services_51557101</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/a-listware/vacancies/363638/?1782420460</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Business Analyst в A-listware, віддалено</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/a-listware/vacancies/363638/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834026-intern-ai-marketing-manager-finerd/</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Intern AI Marketing Manager (finerd)</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834026-intern-ai-marketing-manager-finerd/</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F563"/>
+  <dimension ref="A1:F566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -36349,6 +36445,102 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Analyst III Infrastructure services</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/IND---KA---BANGALORE/Analyst-III-Infrastructure-services_51557101</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>IND - KA - BANGALORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Business Analyst в A-listware, віддалено</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/a-listware/vacancies/363638/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>&lt;h3&gt;Our Customer:&lt;/h3&gt;&lt;p&gt;A global enterprise organization building modern data, analytics, and business process solutions within a Microsoft-first ecosystem. The company focuses on digital transformation, data-driven decision-making, and process optimization through modern analytics and low-code tec</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Intern AI Marketing Manager (finerd)</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834026-intern-ai-marketing-manager-finerd/</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;finerd&lt;/strong&gt; шукає енергійного маркетолога-початківця, якому цікаво розібратись, як запускають продукти, навчитись на реальних задачах і досягти перших ачівментів в кар’єрі.&lt;br /&gt;&lt;br /&gt;&lt;strong&gt;finerd — інвайт-онлі продукт фінансового менеджменту для людей чиї фінанси виходять за межі б</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F566"/>
+  <dimension ref="A1:F570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18514,6 +18514,134 @@
       <c r="F566" t="inlineStr">
         <is>
           <t>2026-06-25 21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>globallogic_f03059cd9001</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/business-analyst-irc296931/</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>novadigital_3cd3714a420f</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Business Analyst (CMS/OMS)</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363644/?lang=en</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/nova-digital/vacancies/363644/?1782456195</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Business Analyst (CMS/OMS) в Nova Digital, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363644/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/789653-finops-analyst/</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>FinOps Analyst</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/789653-finops-analyst/</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F566"/>
+  <dimension ref="A1:F570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -36541,6 +36669,134 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/business-analyst-irc296931/</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>India | Noida | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Business Analyst (CMS/OMS)</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Nova Digital</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363644/?lang=en</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Kyiv, remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Business Analyst (CMS/OMS) в Nova Digital, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/nova-digital/vacancies/363644/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Не просто код, а твій вплив на мільйони українців&lt;/strong&gt; &lt;br /&gt;&lt;strong&gt;Nova Digital&lt;/strong&gt; — це технологічне серце екосистеми &lt;strong&gt;NOVA&lt;/strong&gt;, де твій код стає частиною щоденного життя цілої країни.&lt;br /&gt;&lt;strong&gt;Про масштаб наших сервісів:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;50+ млн запитів щод</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>FinOps Analyst</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/789653-finops-analyst/</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Automat-it is an all-in AWS Premier Partner and Managed Services Provider specializing in the startup ecosystem. With over 800 customers and 500+ AWS certifications, Automat-it brings hands-on expertise in AI, DevOps, and FinOps to empower fast-paced startups to grow, deliver &amp;amp; win. Our custo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F570"/>
+  <dimension ref="A1:F705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18642,6 +18642,4326 @@
       <c r="F570" t="inlineStr">
         <is>
           <t>2026-06-26 06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>epam_52fe453c2228</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Mid-level Calypso Business Analyst</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/mid-level-calypso-business-analyst-blti7i4gc9jw4wrje6u_en</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>epam_2751095675a0</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-engineer-bltqlkev4yo2iny81cz_en</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>epam_6416f03edf98</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-engineer-bltqtv5nkutkqug5k4j_en</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>epam_af575418b320</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>KDB / Quant Developer (Python) - Trading &amp; Analytics Focus</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/kdb-quant-developer-python-trading-analytics-focus-blt9e7l4dxeov96wpjh_en</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>epam_5aa7ea0b32b7</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blto65x6342ng0fezim_en</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>epam_25c450039e6c</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt61938fea8e27a85b_en</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>epam_dd2a82bf304a</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Lead Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-data-analytics-and-visualization-engineer-blt2xo9e4ki87ltpnst_en</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>epam_66371cfbf0e4</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Data Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/data-analytics-product-owner-blth96rh4bzisib3v45_en</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>epam_e38cc190ff5d</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltt17e5ql8vb4n2dig_en</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>epam_097ba959f9d9</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-bltdjo9ak234wy1vifx_en</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>epam_674ef9e7fee1</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blt6wao5qtq5b5kt5oa_en</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>epam_16875f202470</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Lead Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-data-analytics-and-visualization-engineer-bltzmwcm0qlv8xqulqf_en</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>epam_9a715a18a4b6</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blt92e17968d410bf37_en</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>epam_a517f90b8773</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-bltcd2d1ab1d1e5f61e_en</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>epam_72493df16817</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-blt71b0fa8cce292e86_en</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>epam_faced850d1f3</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-blt1d3o3la729rtpy3f_en</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>epam_31c97eb0e668</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltb9hjw7o12t85ybtc_en</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>epam_e21c924d308e</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltcc0f34f9e6e550ad_en</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>epam_b205cf04a413</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant (Data)</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-data-blt7f48f681391e3306_en</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>epam_0ef292ce4ee7</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltkk9uyephyl1iun26_en</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>epam_e018b8de710f</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-developer-blt408430627bbab5cc_en</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>epam_93ec8f669fbc</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltba77fcq5i7dyzjvh_en</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>epam_826612a71b59</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltf1nv3vxqxohxjdbw_en</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>epam_3e47b37b15dd</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltfeotidu8ueofc3a1_en</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>epam_ba8500888431</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltuyu8l4xrxw5xxiay_en</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>epam_62e3f807132a</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltb3kr86q24ek7fz9u_en</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>epam_59891b69b0f4</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt086abe3b46979fcc_en</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>epam_841c5ddd6bd6</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt4c0484d5495fc8e4_en</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>epam_8154b4d32936</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Lead Salesforce CRM Analytics Administrator</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-salesforce-crm-analytics-administrator-blt79z1khxrrw74wron_en</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>epam_4edef15e3ab6</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Senior Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-manager-data-analytics-consulting-blttvb0wrnjyrq5hcte_en</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>epam_9260b5219fb5</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Consultant, Data Analytics</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/consultant-data-analytics-bltz51892wvphm7ws01_en</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>epam_1621e00dd63c</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Data Analytics/AI Consultant (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/data-analytics-ai-consultant-m-f-d-blt4mg7p2ttfcgnahb2_en</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>epam_07fa6ba42fce</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Web Analytics - Adobe</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-software-engineer-web-analytics-adobe-bltw49id05hz4qgvjkg_en</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>epam_b2a2aaa96c86</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer - Web Analytics - Adobe</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-software-engineer-web-analytics-adobe-blte0ij1l8ebtv69lm1_en</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>epam_ca1d3d6bb37b</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Middle Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/middle-data-analytics-and-visualization-engineer-bltbfft7zcqwiffxcsd_en</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>epam_afc14b1cdd06</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltau9qydydlakn3l3r_en</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>epam_aa24f1986031</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltizj24pdk53xya5jz_en</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>epam_bc91884411b2</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt1lvpfwezd3vkq3n3_en</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>epam_71597ab5c2f9</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt3xyr85q90661dw2k_en</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>epam_194bcbe555bb</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt9uszrhqloo3w143i_en</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>epam_360912be05d4</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-blt1bvno44rx0tha9xz_en</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>epam_af4f68affc1e</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltme0mjm0mh5j44wmh_en</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>epam_272d118741fd</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltsb27b316qpmx3gjt_en</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>epam_38bbd70e8692</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltv7xbn7824xbeugmc_en</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>globallogic_555131980a4a</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/business-analyst-product-owner-irc298701/</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>globallogic_780a25f66af2</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Associate Analyst</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/associate-analyst-irc298603/</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>globallogic_914f82208d33</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298680/</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>globallogic_1360761ece1f</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Senior/Lead Business Analyst for Energy program</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/senior-lead-business-analyst-for-energy-program-irc298773/</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>globallogic_3cd3dcd5334d</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>dbt Architect/ Lead Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/dbt-architect-lead-analytics-engineer-irc297840/</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>globallogic_1506542776cf</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/data-analytics-architect-irc293853/</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>softserve_9afa90ffb909</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Advanced Analytics)</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/senior-data-scientist-advanced-analytics-88739</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>softserve_ae43e6d4d2eb</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Advanced Analytics)</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/senior-data-scientist-advanced-analytics-88738</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>dataart_8f3a59e20117</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Business Analyst with Buy-Side and Front Office Experience</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/dan00088</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>dataart_f07ca4fff226</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Data Engineer with BigQuery and Dataform, Analytics Platform</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00307</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>dataart_cea2057aa773</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Data Engineer with Analytics</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00282</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>dataart_07f39c7a8ed3</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Senior Analytics &amp; AI Engineer (Power BI, Data Platforms &amp; Azure AI)</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00304</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>wix_a50a1810994f</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Revenue Operations Manager - Base44</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Wix</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Wix2/744000132184838</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Wix</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>SKELAR_642a277c38e4</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Analytics Team Lead - Agen</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/631c6884-7881-4218-810a-2e5352ef9c7f</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>SKELAR_fa5b1235d4a8</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Growth Manager (Monetization) - Dressly</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/59254e1e-500e-4823-9cd8-6f44c972d041</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>SKELAR_4050f844f48a</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Marketing Specialist (Switch to Product Marketing Manager)</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/153c9712-8e16-41cb-9d34-ea16dbd02f31</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>SKELAR_dedaaf427c39</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>YouTube Growth Manager - RiseGuide</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/d0f87771-587a-4af3-88ed-669e89da88b2</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Ajax_8b54d1d1781a</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Head of Financial Planning &amp; Analytics Department</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Ajax Systems</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/ajax/12248a05-3290-4793-bf0c-968f51bb0e49</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>DXC_f91706ef6844</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>SAP Senior Analytics Consultant - SAP Analytics Cloud &amp; Datasphere</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/POL---MZ---WARSAW/SAP-Senior-Analytics-Consultant---SAP-Analytics-Cloud---Datasphere_51572422</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>DXC_a3ef54a6a087</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Senior SAP (BW/BI) Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/SVK---BL---BRATISLAVA/Senior-SAP-Analytics-Consultant_51580415</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>DXC_b0beb7d7122a</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Senior SAP BW Analytics Consultant with German</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/POL---MZ---WARSAW/Senior-SAP-BW-Analytics-Consultant-with-German_51581530-1</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>DXC_eb4b55310870</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Junior BI Consultant - Data Warehouse &amp; Analytics (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/AUT---VIENNA/Junior-BI-Consultant---Data-Warehouse---Analytics--f-m-d-_51582962</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>tieto_941de4f00bcb</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics ProjectÂ ManagerÂ â Tieto Tech Consulting (m/f/d)Â</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>https://careers.tieto.com/job/data-and-analytics-project-manager-tieto-tech-consulting-m-f-d-in-espoo-finland-jid-2559</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>griddynamics_2cabe3ad33df</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Data Analyst- Python, ML</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/49901</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>griddynamics_61a62598a62c</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/54497</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>griddynamics_2f2224ba3f6d</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Safety Insights Analyst with Italian language</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/57325</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>griddynamics_1a12a64b1977</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Senior FinOps / Infrastructure Cost Analyst</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/54866</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>griddynamics_53ccd18c95ab</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Staff Data Analyst with Italian</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/51220</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>griddynamics_cf12e5e5f44a</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Data Analyst with French</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/46963</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>griddynamics_76170452bfc0</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety Insights (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52095</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>griddynamics_27c090f89232</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/23782</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>griddynamics_5398a77b7db0</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/38597</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>griddynamics_c3dfe55a3cd7</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Data Analyst with German</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/46397</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>griddynamics_812e83351f84</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52096</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>griddynamics_a328020bf3ac</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52028</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>griddynamics_b001c849f8cc</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety Insights (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52101</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>avenga_a9d82f937ead</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7878317-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>avenga_f09c5fb63c89</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7853365-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>avenga_25ea373af707</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7737764-it-business-analyst</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>avenga_247c0757d1af</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7564298-business-analyst</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>avenga_59358ff68831</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7331976-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>avenga_6f82048deab6</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7237222-senior-business-analyst</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>avenga_ffb6d008c889</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7217755-senior-business-analyst</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>avenga_90ec51cb149f</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7138167-product-analyst</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>avenga_4798bc7c4e05</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5617994-it-business-analyst</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>avenga_bf7ce421be6c</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5598258-it-business-analyst</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>avenga_501902186512</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5597677-data-analyst</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>betterme_3ab89a0b85a5</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Data Analyst (Performance Marketing)</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BetterMe</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>https://betterme.breezy.hr/p/7985c451c2dd-data-analyst-performance-marketing</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>BetterMe</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>OBRIO_158d3c00b2ae</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analyst </t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/29c55022-37dd-4fec-9eda-e0ab0f6baf07</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>OBRIO_569269581930</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analyst (Marketing) </t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/6a95fb7e-ec05-465f-8e65-8e90c14f96e8</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>OBRIO_0e16e2db0524</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Product Analyst (Content)</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/e0cbde36-a0b3-4df6-8da0-993dc80ea2e3</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>allstarsit_328a56467a53</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>AllStarsIT</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>https://www.allstarsit.com/job-posts/senior-data-analyst-windward</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>AllStarsIT</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>autodoc_a0380bc4f470</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Integrations Analyst</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000133901379</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>autodoc_d09fc5fc6d70</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Integrations Analyst</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000132235949</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>autodoc_7a76f3ffd8f9</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000125093710</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>autodoc_0df93ff6f422</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000125094298</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>autodoc_d14923a6c2d1</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Business Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000120864577</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/agiliway/vacancies/363696/?1782469779</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Middle SOC Analyst/ SecOps Engineer в Agiliway, віддалено</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/agiliway/vacancies/363696/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/metinvest-digital/vacancies/363685/?1782467446</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Аналітик з інцидентів в Metinvest Digital, віддалено</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/metinvest-digital/vacancies/363685/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/novapay/vacancies/363682/?1782466120</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>AI Business Analyst в NovaPay, віддалено</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/novapay/vacancies/363682/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/zeely-ai/vacancies/266385/?1782461600</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Senior Product Analyst в Zeely AI, віддалено</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zeely-ai/vacancies/266385/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/1plus1/vacancies/355442/?1782460009</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Business Analyst (Kyivstar TV) в 1+1 media, Київ</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/1plus1/vacancies/355442/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/otp-bank-ukraine/vacancies/359402/?1782459616</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Business Analyst в OTP Bank Ukraine, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/otp-bank-ukraine/vacancies/359402/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/fractal-analytics/vacancies/265608/?1780569862</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Power BI developer в Fractal Analytics, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/fractal-analytics/vacancies/265608/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/it-smartflex/vacancies/360353/?1780391549</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Power BI Developer \ Analytics Engineer (Microsoft Fabric) в IT SmartFlex, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/it-smartflex/vacancies/360353/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/epc-network/vacancies/362856/?1781872384</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Data Analyst/Broadcast Manager (Warsaw or Kyiv) в EPC Network, Київ, Варшава (Польща)</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/epc-network/vacancies/362856/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/whitebit/vacancies/315220/?1782302392</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Financial Manager for Analytics and Control (Relocate, office work) в WhiteBIT, за кордоном</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/whitebit/vacancies/315220/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/solidgate/vacancies/263532/?1781786100</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Junior Business Analyst (Account Management and Sales team) в Solidgate, Київ</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/solidgate/vacancies/263532/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/fulcrum/vacancies/350234/?1781534037</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в Fulcrum, віддалено</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/fulcrum/vacancies/350234/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/demch-co/vacancies/320887/?1781530873</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Project Manager / Business Analyst в Demch.co, до&amp;nbsp;$2000, віддалено</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/demch-co/vacancies/320887/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/zfort/vacancies/362052/?1781278957</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в ZFORT Group, Харків, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zfort/vacancies/362052/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/cs-ltd/vacancies/352588/?1780936122</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Координатор відділу Business Analysts (Resource / Project Manager) в CS Ltd, віддалено</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/cs-ltd/vacancies/352588/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/glorium-technologies-corp/vacancies/360979/?1780650125</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Senior AI Business Analyst в Glorium Technologies, Пафос (Кіпр), віддалено</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/glorium-technologies-corp/vacancies/360979/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/mgid/vacancies/360938/?1780604282</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Commercial Analytics &amp;amp; Insights Senior Manager в MGID, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mgid/vacancies/360938/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/mticket/vacancies/360663/?1780490409</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Senior AI Workflow Automation Business Analyst в Mticket, віддалено</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mticket/vacancies/360663/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/prytulafoundation/vacancies/352966/?1780307857</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Спеціаліст, аналітик з тестування FPV-засобів, Київ в Благодійний фонд Сергія Притули, Київ</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/prytulafoundation/vacancies/352966/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/adaptiq/vacancies/354007/?1779794342</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Researcher / Analyst в Adaptiq, віддалено</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/adaptiq/vacancies/354007/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/funteron/vacancies/359510/?1779788842</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Business Analyst в Funteron, Львів</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/funteron/vacancies/359510/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/promin-apps/vacancies/355118/?1782473142</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (Senior) в Promin Apps, віддалено</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/promin-apps/vacancies/355118/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/viseven/vacancies/363671/?1782463741</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (B2B) в Viseven Group, віддалено</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/viseven/vacancies/363671/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/growity-tech/vacancies/346966/?1782460757</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Creative Marketing Manager в Growity Tech, віддалено</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/growity-tech/vacancies/346966/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/choice/vacancies/363660/?1782460569</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Senior Marketing Manager (B2B SAAS) в CHOICE, $1500–2000, віддалено</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/choice/vacancies/363660/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/833905-data-analytics-mentor-part-time/</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Data Analytics Mentor (part-time)</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833905-data-analytics-mentor-part-time/</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/831098-cyber-security-analyst/</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Cyber Security Analyst</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831098-cyber-security-analyst/</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/822101-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/822101-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/819839-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/819839-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/803701-growth-marketing-manager-health-and-fitness-a/</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager (Health and Fitness app)</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/803701-growth-marketing-manager-health-and-fitness-a/</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/831313-business-analyst-french-speaking/</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Business Analyst (French-speaking)</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831313-business-analyst-french-speaking/</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834134-business-analyst-product-owner/</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834134-business-analyst-product-owner/</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834133-odoo-business-analyst/</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Odoo Business Analyst</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834133-odoo-business-analyst/</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834132-senior-lead-data-analyst-wellbeing-product/</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Senior/Lead Data Analyst (Wellbeing product)</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834132-senior-lead-data-analyst-wellbeing-product/</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
         </is>
       </c>
     </row>
@@ -18656,7 +22976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F570"/>
+  <dimension ref="A1:F705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -36797,6 +41117,4261 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Mid-level Calypso Business Analyst</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/mid-level-calypso-business-analyst-blti7i4gc9jw4wrje6u_en</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-engineer-bltqlkev4yo2iny81cz_en</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-engineer-bltqtv5nkutkqug5k4j_en</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Lviv, Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>KDB / Quant Developer (Python) - Trading &amp; Analytics Focus</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/kdb-quant-developer-python-trading-analytics-focus-blt9e7l4dxeov96wpjh_en</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blto65x6342ng0fezim_en</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt61938fea8e27a85b_en</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Lead Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-data-analytics-and-visualization-engineer-blt2xo9e4ki87ltpnst_en</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Data Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/data-analytics-product-owner-blth96rh4bzisib3v45_en</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltt17e5ql8vb4n2dig_en</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-bltdjo9ak234wy1vifx_en</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blt6wao5qtq5b5kt5oa_en</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Lead Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-data-analytics-and-visualization-engineer-bltzmwcm0qlv8xqulqf_en</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-blt92e17968d410bf37_en</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-data-analytics-and-visualization-engineer-bltcd2d1ab1d1e5f61e_en</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-blt71b0fa8cce292e86_en</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-blt1d3o3la729rtpy3f_en</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltb9hjw7o12t85ybtc_en</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltcc0f34f9e6e550ad_en</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant (Data)</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-data-blt7f48f681391e3306_en</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Turkiye</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltkk9uyephyl1iun26_en</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-developer-blt408430627bbab5cc_en</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltba77fcq5i7dyzjvh_en</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltf1nv3vxqxohxjdbw_en</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltfeotidu8ueofc3a1_en</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltuyu8l4xrxw5xxiay_en</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Business Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/business-analytics-consultant-bltb3kr86q24ek7fz9u_en</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt086abe3b46979fcc_en</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Lviv, Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/senior-data-analytics-and-visualization-engineer-blt4c0484d5495fc8e4_en</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Lead Salesforce CRM Analytics Administrator</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-salesforce-crm-analytics-administrator-blt79z1khxrrw74wron_en</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Senior Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-manager-data-analytics-consulting-blttvb0wrnjyrq5hcte_en</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Melbourne, Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Consultant, Data Analytics</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/consultant-data-analytics-bltz51892wvphm7ws01_en</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Data Analytics/AI Consultant (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/data-analytics-ai-consultant-m-f-d-blt4mg7p2ttfcgnahb2_en</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Web Analytics - Adobe</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-software-engineer-web-analytics-adobe-bltw49id05hz4qgvjkg_en</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer - Web Analytics - Adobe</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/lead-software-engineer-web-analytics-adobe-blte0ij1l8ebtv69lm1_en</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Middle Data Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/ua/vacancy/middle-data-analytics-and-visualization-engineer-bltbfft7zcqwiffxcsd_en</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltau9qydydlakn3l3r_en</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Manager, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/manager-data-analytics-consulting-bltizj24pdk53xya5jz_en</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt1lvpfwezd3vkq3n3_en</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt3xyr85q90661dw2k_en</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Managing Principal / Senior Director, Data Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/managing-principal-senior-director-data-analytics-consulting-blt9uszrhqloo3w143i_en</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-blt1bvno44rx0tha9xz_en</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltme0mjm0mh5j44wmh_en</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltsb27b316qpmx3gjt_en</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Principal/Director, Data Analytics Consulting for Financial Services</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/principal-director-data-analytics-consulting-for-financial-services-bltv7xbn7824xbeugmc_en</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/business-analyst-product-owner-irc298701/</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Associate Analyst</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/associate-analyst-irc298603/</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Gurgaon | India | On-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Ice Hockey Analyst</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/ice-hockey-analyst-irc298680/</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Senior/Lead Business Analyst for Energy program</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/senior-lead-business-analyst-for-energy-program-irc298773/</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>dbt Architect/ Lead Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/dbt-architect-lead-analytics-engineer-irc297840/</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>London | United Kingdom | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>GlobalLogic</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>https://www.globallogic.com/careers/data-analytics-architect-irc293853/</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Ukraine | Remote | On-site | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Advanced Analytics)</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/senior-data-scientist-advanced-analytics-88739</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Technology | Colombia; Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Advanced Analytics)</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/senior-data-scientist-advanced-analytics-88738</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Technology | Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Business Analyst with Buy-Side and Front Office Experience</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/dan00088</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>As a Business Analyst for a top‑20 global investment firm, you will work on projects that enhance data availability and accuracy across the investment platform. You will collaborate with portfolio managers, product teams, and the data workstream to address complex data issues and deliver solutions t</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Data Engineer with BigQuery and Dataform, Analytics Platform</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00307</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>This project focuses on building a scalable and reliable data platform that powers analytics, reporting, and data driven decision making across the organization. You will help integrate multiple enterprise data sources and ensure consistent, high quality data delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Data Engineer with Analytics</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00282</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>We are looking for a Data Engineer with a strong technical background and a deep understanding of the data lifecycle, from acquisition and integration to modeling and exploitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Senior Analytics &amp; AI Engineer (Power BI, Data Platforms &amp; Azure AI)</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>https://www.dataart.team/vacancies/de00304</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>We are seeking a Senior Analytics &amp; AI Engineer to help optimize and evolve enterprise analytics solutions built on Power BI, SQL Server, and modern data platforms while enabling AI-driven analytics experiences using Azure AI technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Revenue Operations Manager - Base44</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Wix</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Wix</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Wix2/744000132184838</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Tel Aviv, il</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Analytics Team Lead - Agen</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/631c6884-7881-4218-810a-2e5352ef9c7f</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Kyiv | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Growth Manager (Monetization) - Dressly</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/59254e1e-500e-4823-9cd8-6f44c972d041</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Ukraine, Remote | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Marketing Specialist (Switch to Product Marketing Manager)</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/153c9712-8e16-41cb-9d34-ea16dbd02f31</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Kyiv | OnSite</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>YouTube Growth Manager - RiseGuide</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>SKELAR</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/SKELAR/d0f87771-587a-4af3-88ed-669e89da88b2</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Kyiv | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Head of Financial Planning &amp; Analytics Department</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Ajax Systems</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/ajax/12248a05-3290-4793-bf0c-968f51bb0e49</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Ajax Systems — міжнародна технологічна компанія і найбільший у Європі виробник охоронних систем. Продуктам Ajax довіряють уже понад 4,5 мільйони кінцевих користувачів і 330 тисяч PRO-користувачів у більш ніж 180 країнах. Компанія пропонує комплексні рішення для захисту житлових і комерційних об'єкті</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>SAP Senior Analytics Consultant - SAP Analytics Cloud &amp; Datasphere</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/POL---MZ---WARSAW/SAP-Senior-Analytics-Consultant---SAP-Analytics-Cloud---Datasphere_51572422</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>5 Locations</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Senior SAP (BW/BI) Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/SVK---BL---BRATISLAVA/Senior-SAP-Analytics-Consultant_51580415</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>SVK - BL - BRATISLAVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Senior SAP BW Analytics Consultant with German</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/POL---MZ---WARSAW/Senior-SAP-BW-Analytics-Consultant-with-German_51581530-1</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>4 Locations</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Junior BI Consultant - Data Warehouse &amp; Analytics (f/m/d)</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/AUT---VIENNA/Junior-BI-Consultant---Data-Warehouse---Analytics--f-m-d-_51582962</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>AUT - VIENNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics ProjectÂ ManagerÂ â Tieto Tech Consulting (m/f/d)Â</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>TietoEVRY</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>https://careers.tieto.com/job/data-and-analytics-project-manager-tieto-tech-consulting-m-f-d-in-espoo-finland-jid-2559</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Data Analyst- Python, ML</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/49901</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Canada Remote, Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/54497</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>US Remote, US</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Safety Insights Analyst with Italian language</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/57325</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:28</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Senior FinOps / Infrastructure Cost Analyst</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/54866</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Kyiv, Kharkiv, Lviv, Dnipro, Vinnytsia, Odesa, Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Staff Data Analyst with Italian</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/51220</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Kyiv, Lviv, Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Data Analyst with French</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/46963</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety Insights (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52095</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/23782</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Canada Remote, Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/38597</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Dublin, Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Data Analyst with German</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/46397</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52096</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52028</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Chisinau, Moldova</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Middle/Senior Safety Insights (Data) Analyst</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Grid Dynamics</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>https://www.griddynamics.com/careers/vacancy/52101</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>West Europe Remote, West Europe Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7878317-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7853365-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7737764-it-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7564298-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7331976-senior-business-analyst-product-owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7237222-senior-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7217755-senior-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/7138167-product-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5617994-it-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>IT Business Analyst</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5598258-it-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Avenga</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>https://career.avenga.com/jobs/5597677-data-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Data Analyst (Performance Marketing)</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BetterMe</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>BetterMe</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>https://betterme.breezy.hr/p/7985c451c2dd-data-analyst-performance-marketing</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analyst </t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/29c55022-37dd-4fec-9eda-e0ab0f6baf07</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Remote – Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analyst (Marketing) </t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/6a95fb7e-ec05-465f-8e65-8e90c14f96e8</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Remote – Ukraine | Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Product Analyst (Content)</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>OBRIO</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/OBRIO/e0cbde36-a0b3-4df6-8da0-993dc80ea2e3</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Kyiv (Office) | Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>AllStarsIT</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>AllStarsIT</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>https://www.allstarsit.com/job-posts/senior-data-analyst-windward</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Integrations Analyst</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000133901379</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Lisbon, pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Integrations Analyst</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000132235949</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Chișinău, md</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000125093710</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Chișinău, md</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000125094298</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Lisbon, pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Business Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Autodoc</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Autodoc3/744000120864577</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Szczecin, pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Middle SOC Analyst/ SecOps Engineer в Agiliway, віддалено</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/agiliway/vacancies/363696/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for a Middle SOC Analyst/SecOps Engineer to join our team in testing a cybersecurity vulnerability product for our client based in the USA and Canada. Our client is a globally recognized SaaS company operating in the healthcare domain and dedicated to improving hearing care worldwi</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Аналітик з інцидентів в Metinvest Digital, віддалено</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/metinvest-digital/vacancies/363685/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Шукаємо &lt;strong&gt;АНАЛІТИКА з ІНЦИДЕНТІВ до команди Центру кібербезпеки!&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Готовий працювати з реальними кіберзагрозами, а не теорією? У Центрі кібербезпеки Metinvest Digital ти будеш щодня аналізувати інциденти, розслідувати атаки та впливати на безпеку великого міжнародного бізнесу. </t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>AI Business Analyst в NovaPay, віддалено</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/novapay/vacancies/363682/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;NovaPay &lt;/strong&gt;— міжнародний фінансовий сервіс, що входить в ГК NOVA.&lt;br /&gt;&lt;br /&gt;Ми створюємо сучасні платіжні рішення для бізнесу та мільйонів користувачів. Розвиваємо власну платіжну систему, мобільний застосунок і пропонуємо широкий спектр продуктів і послуг як офлайн — у відділеннях</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Senior Product Analyst в Zeely AI, віддалено</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zeely-ai/vacancies/266385/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Zeely AI &lt;/strong&gt;— це платформа, яка за допомогою штучного інтелекту генерує вірусні UGC-відео та рекламні банери, а також запускає ефективні рекламні кампанії у Facebook та Instagram, допомагаючи малому бізнесу ставати помітним і зростати.&lt;br /&gt;&lt;br /&gt;Маємо вже понад 1 млн. користувачів </t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Business Analyst (Kyivstar TV) в 1+1 media, Київ</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/1plus1/vacancies/355442/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Київстар ТБ &lt;/strong&gt;запрошує &lt;strong&gt;Business Analyst&lt;/strong&gt; аби забезпечувати розвиток проєктів і супроводжувати робочі процеси в компанії. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;Вам до нас, якщо Ви:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;бажаєте працювати над власним продуктом, на результат, який можна виміряти;&lt;/li&gt;&lt;li&gt;маєте</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Business Analyst в OTP Bank Ukraine, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/otp-bank-ukraine/vacancies/359402/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;OTP Bank Україна&lt;/strong&gt; — один з найбільших українських банків зі 100%-им іноземним капіталом, визнаний лідер фінансового сектору країни, член європейської фінансової групи, що працює в 11 країнах.&lt;br /&gt;&lt;br /&gt;Друзі, наразі ми знаходимося у пошуку &lt;strong&gt;Business Analyst.&lt;/strong&gt;&lt;/p&gt;&lt;p</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Power BI developer в Fractal Analytics, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/fractal-analytics/vacancies/265608/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;About Us:&lt;/strong&gt; Fractal is a dynamic and innovative AI company that is committed to delivering cutting-edge solutions to our clients. We are currently seeking a talented and experienced Power BI developer to join our growing team.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Responsibilities:&lt;/strong&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Le</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Power BI Developer \ Analytics Engineer (Microsoft Fabric) в IT SmartFlex, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/it-smartflex/vacancies/360353/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Ми — &lt;strong&gt;IT SmartFlex&lt;/strong&gt;, українська ІТ компанія, заснована в 2019 році як дочірня компанія провідного мобільного оператора Vodafone Ukraine.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;🌟 Наша місія&lt;/strong&gt; — об’єднати талановитих експертів у телекомунікаціях та програмному забезпеченні, щоб створювати інноваційні </t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Data Analyst/Broadcast Manager (Warsaw or Kyiv) в EPC Network, Київ, Варшава (Польща)</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/epc-network/vacancies/362856/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Location:&lt;/b&gt; Warsaw/Kyiv office&lt;br /&gt;&lt;b&gt;Format:&lt;/b&gt; Full-time&lt;br /&gt;&lt;b&gt;Type of contract:&lt;/b&gt; B2B&lt;br /&gt;&lt;b&gt;Seniority:&lt;/b&gt; Middle&lt;br /&gt;&lt;b&gt;English level:&lt;/b&gt; В1+&lt;/p&gt;&lt;p&gt;&lt;b&gt;About Us&lt;/b&gt; &lt;br /&gt;At EPC Network, we’re not just a digital marketing company; we’re a platform for career transformation and p</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Financial Manager for Analytics and Control (Relocate, office work) в WhiteBIT, за кордоном</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/whitebit/vacancies/315220/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are the creators of a new fintech era!&lt;br /&gt;Our mission is to change this world by making blockchain accessible to everyone in everyday life. WhiteBIT is a global team of over 1,200 professionals united by one mission — to shape the new world order in the Web3 era. Each of our employees is ful</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Junior Business Analyst (Account Management and Sales team) в Solidgate, Київ</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/solidgate/vacancies/263532/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h3&gt;&lt;b&gt;Our Mission and Vision&lt;/b&gt;&lt;/h3&gt;&lt;p&gt;At Solidgate, our mission is clear: to empower outstanding entrepreneurs to build exceptional internet companies. We exist to fuel the builders — the ones shaping the digital economy — with the financial infrastructure they deserve. To achieve that, we’re on </t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в Fulcrum, віддалено</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/fulcrum/vacancies/350234/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>&lt;h3&gt;&lt;/h3&gt;&lt;p&gt;About &lt;strong&gt;Fulcrum&lt;/strong&gt;: We’re a team of tech-savvy, creative &amp;amp; passionate IT professionals. We’ve created a vibrant and performance-driven culture for ourselves where everyone is free to think &amp;amp; act outside the box. There are literally no limits to what you can do here, a</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Project Manager / Business Analyst в Demch.co, до&amp;nbsp;$2000, віддалено</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/demch-co/vacancies/320887/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;&lt;a href="http://demch.co" target="_blank"&gt;demch.co&lt;/a&gt;&lt;/b&gt; — це не просто вебстудія. Ми команда професіоналів, яка допомагає неприбутковим організаціям, як громадським так державним ініціативам, що працюють над суспільними змінами, розкривати свій цифровий потенціал.&lt;/p&gt;&lt;p&gt;Ми шукаємо &lt;b&gt;Projec</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Project Manager/Business Analyst в ZFORT Group, Харків, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zfort/vacancies/362052/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are looking for &lt;strong&gt;Middle-Senior Project Manager/Business Analyst&lt;/strong&gt; to join our team.&lt;br /&gt;&lt;strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Required Skills &amp;amp; Qualifications:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;— 7+ years of proven project management experience&lt;br /&gt;— 4+ years of business analysis and requirements m</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Координатор відділу Business Analysts (Resource / Project Manager) в CS Ltd, віддалено</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/cs-ltd/vacancies/352588/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Українська продуктова та сервісна IT-компанія&lt;strong&gt; CS &lt;/strong&gt;у пошуку &lt;strong&gt;Координатора відділу Business Analysts&lt;/strong&gt; з досвідом Resource / Project Manager.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Навички та досвід:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Досвід роботи у ролі Project Manager / Resource Manager в IT від 1 року;&lt;/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Senior AI Business Analyst в Glorium Technologies, Пафос (Кіпр), віддалено</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/glorium-technologies-corp/vacancies/360979/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The design and product workflow is changing — and this role sits right at the center of that shift. You’ll lead a client-facing engagement where the goal is to replace a traditional Figma-first process with an AI-native prototyping practice. That means turning live client conversations into worki</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Commercial Analytics &amp;amp; Insights Senior Manager в MGID, Київ, за кордоном, віддалено</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mgid/vacancies/360938/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;MGID&lt;/strong&gt; is a global native advertising platform that helps brands reach unique local audiences at scale. At MGID, we empower brands and publishers to collaborate transparently through our privacy-first targeting technology. This enables advertisers to drive performance and awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Senior AI Workflow Automation Business Analyst в Mticket, віддалено</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mticket/vacancies/360663/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h3&gt;About the Role&lt;/h3&gt;&lt;p&gt;MTicket is looking for a &lt;strong&gt;Senior AI Workflow Automation Business Analyst&lt;/strong&gt; to help transform the way event operations are planned, managed, and optimized through intelligent automation and AI agents.&lt;br /&gt;In the event industry, every stage of the lifecycle is </t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Спеціаліст, аналітик з тестування FPV-засобів, Київ в Благодійний фонд Сергія Притули, Київ</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/prytulafoundation/vacancies/352966/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;b&gt;Благодійний фонд Сергія Притули&lt;/b&gt; — це неприбуткова благодійна організація, яка була заснована у 2020 році Сергієм Притулою разом із командою. Фонд було створено з метою надання допомоги медичним працівникам, особам з інвалідністю, розвитку напрямів освіти та інклюзії та підтримки вразливих </t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Researcher / Analyst в Adaptiq, віддалено</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/adaptiq/vacancies/354007/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Who we are:&lt;/b&gt;&lt;/p&gt;&lt;p&gt;Adaptiq is a technology hub specializing in building, scaling, and supporting R&amp;amp;D teams for high-end, fast-growing product companies in a wide range of industries. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About the Role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We’re looking for a &lt;b&gt;Researcher /</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Business Analyst в Funteron, Львів</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/funteron/vacancies/359510/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Funteron is an AI-powered sports engagement platform that enables trusted media brands to offer embedded odds comparison and betting experiences across multiple licensed sportsbook operators.&lt;br /&gt;&lt;strong&gt;We are opening an office in Lviv, Ukraine and building our first team here.&lt;/strong&gt; &lt;br /&gt;&lt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (Senior) в Promin Apps, віддалено</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/promin-apps/vacancies/355118/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Promin Apps&lt;/b&gt; is a product-first company on a mission to help people feel better, move more, and live healthier lives — physically and emotionally.&lt;br /&gt;&lt;br /&gt;At the intersection of AI, data, behavioral science, and personalization, we build thoughtful digital products that support fundament</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager (B2B) в Viseven Group, віддалено</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/viseven/vacancies/363671/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Місія ролі&lt;/strong&gt; &lt;br /&gt;&lt;br /&gt;На цій посаді ви підтримуватимете розвиток Product Marketing у Viseven, допомагаючи перетворювати інформацію про продукти на зрозумілі повідомлення та маркетингові матеріали, які дозволяють командам продажів ефективно доносити цінність наших рішень для кліє</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Creative Marketing Manager в Growity Tech, віддалено</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/growity-tech/vacancies/346966/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are &lt;b&gt;Growity Tech&lt;/b&gt;, a product company building products that move people forward. We bring together a global team of experts to solve complex challenges and turn strong ideas into measurable impact for millions of users.&lt;/p&gt;&lt;p&gt;We are seeking an ambitious and skilled&lt;strong&gt; Creative Marke</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Senior Marketing Manager (B2B SAAS) в CHOICE, $1500–2000, віддалено</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/choice/vacancies/363660/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Про нас:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Choice&lt;/strong&gt; — це провідна європейська food-tech B2B SaaS-платформа. Ми допомагаємо &lt;strong&gt;понад 30 000+ ресторанам у 20 країнах &lt;/strong&gt;збільшувати прибутки завдяки єдиній цифровій екосистемі: QR-платежам, онлайн-резервуванню та управлінню доставкою. </t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Data Analytics Mentor (part-time)</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/833905-data-analytics-mentor-part-time/</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are &lt;strong&gt;Mate academy,&lt;/strong&gt; an EdTech startup with a tech-driven, gamified, AI-friendly LMS platform where people learn IT specialties.&lt;br /&gt;You can explore our platform &lt;a href="https://mate.academy/pl" target="_blank"&gt;here.&lt;/a&gt; &lt;/p&gt;&lt;p&gt;&lt;strong&gt;🌎Our mission&lt;/strong&gt; is to help a million</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Cyber Security Analyst</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831098-cyber-security-analyst/</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We’re seeking motivated, sharp-minded professionals to join our team as a Cyber Security Analyst/Researcher. In this role, you’ll collaborate directly with clients, examine traffic patterns, and play a key part in identifying and neutralizing harmful bots and online threats.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;s</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/822101-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Boosty&lt;/strong&gt; is a company specializing in the sale of dietary supplements. Our mission is to simplify people's lives by helping them use fewer but more effective products. We strive to build a community that aspires to live long and healthy lives.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Our products contai</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/819839-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;🚀 About Awesomic&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are a web app that matches businesses from around the world with the best-fit talents using an AI-driven algorithm. Since our founding in 2020, we’ve completed 14,000+ tasks for 4,000+ clients, including Reface, Lift99, SilviaTerra, Y Combinator startups</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager (Health and Fitness app)</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/803701-growth-marketing-manager-health-and-fitness-a/</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Привіт!&amp;nbsp;&lt;br /&gt;Запрошуємо &lt;strong&gt;Growth Marketing Manager&lt;/strong&gt;-а, який буде owner конверсії в покупку у web/web2app-флоу та відповідатиме за її зростання через системне A/B тестування та data-driven рішення, приєднатися до партнерської компанії.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Основний фокус ро</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Business Analyst (French-speaking)</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/831313-business-analyst-french-speaking/</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;About the Project&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are launching an international digital transformation project focused on the modernization and migration of a national geospatial data platform. The platform serves as a central repository for geospatial information, open data, maps, and climate resilie</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834134-business-analyst-product-owner/</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;A program of projects within the Energy domain. We will work on various applications covering generation control, distribution control, transmission control, and service crews control. The implementation area of these products is very high-scale (e.g. country-wide systems).&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;strong&gt;Re</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Odoo Business Analyst</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834133-odoo-business-analyst/</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;br /&gt;&lt;strong&gt;Kiss My Apps&lt;/strong&gt; — компанія-платформа, що об’єднує 7 продуктових вертикалей та 30+ AI-first продуктів, 100+ мільйонів користувачів, власну екосистему аналітичних, пеймент та маркетингових розробок.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Продукти KMA це світові лідери в нішах utilities, lifestyle, </t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Senior/Lead Data Analyst (Wellbeing product)</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834132-senior-lead-data-analyst-wellbeing-product/</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;Kiss My Apps&lt;/strong&gt; — компанія-платформа, що об’єднує 7 продуктових вертикалей та 30+ AI-first продуктів, 100+ мільйонів користувачів, власну екосистему аналітичних, пеймент та маркетингових розробок.&lt;/p&gt;&lt;p&gt;Продукти KMA це світові лідери в нішах utilities, lifestyle, health&amp;amp;fitness </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F705"/>
+  <dimension ref="A1:F725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22962,6 +22962,646 @@
       <c r="F705" t="inlineStr">
         <is>
           <t>2026-06-26 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>epam_2464db3a5fa2</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltysm67aqe7dfb6hsp_en</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>epam_1ac8215575b0</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltmhaw7caik59u0b5p_en</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>epam_dfb60ebdaaf8</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltnun7kccr749a49he_en</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>epam_37f6babbb633</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltxsu7c24u0501l7qa_en</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>epam_d9c7c38d88b0</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-blt951fvvh01be9nvck_en</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>epam_220fc22a7883</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Mid-level Calypso Business Analyst</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/mid-level-calypso-business-analyst-bltdeazs0xwp2w76h4y_en</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>zone3000_ffd52f3c7e12</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analyst in Marketing Analyst Team (#1194)</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Zone3000</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>https://zone3000.net/vacancies/senior-marketing-analyst-in-marketing-analyst-team---1194-</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Zone3000</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/ab3/vacancies/363773/?1782485118</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Проектний аналітик в Третій армійський корпус, від&amp;nbsp;$1000</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ab3/vacancies/363773/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/yasno/vacancies/363762/?1782482440</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик в YASNO, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/yasno/vacancies/363762/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/ukrsibbank/vacancies/363753/?1782481170</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Аналітик процесів в UKRSIBTECH, Київ</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ukrsibbank/vacancies/363753/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/zone3000/vacancies/363749/?1782480714</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analyst in Marketing Analyst Team (#1194) в ZONE3000, віддалено</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zone3000/vacancies/363749/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/appflame/vacancies/363744/?1782480147</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Middle Product Analyst (Growth direction) в appflame, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/appflame/vacancies/363744/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/quarks-tech/vacancies/352129/?1782477931</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Product Analyst в Quarks, Київ, гібрид, Київ, Варшава (Польща), віддалено</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/quarks-tech/vacancies/352129/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?1782483838</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager в Око Камера, Київ</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/blyskavka/vacancies/363728/?1782478130</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Marketing Manager в BLYSKAVKA, $1000–1200, Київ</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/blyskavka/vacancies/363728/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834231-analitik/</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Аналітик</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834231-analitik/</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834220-growth-marketing-manager-head-of-growth/</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager/Head of Growth</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834220-growth-marketing-manager-head-of-growth/</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834183-system-business-analyst/</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>System / Business Analyst</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834183-system-business-analyst/</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/832715-data-analyst/</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/832715-data-analyst/</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/832718-business-analyst/</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/832718-business-analyst/</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
         </is>
       </c>
     </row>
@@ -22976,7 +23616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F705"/>
+  <dimension ref="A1:F725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -45372,6 +46012,646 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltysm67aqe7dfb6hsp_en</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltmhaw7caik59u0b5p_en</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltnun7kccr749a49he_en</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-bltxsu7c24u0501l7qa_en</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/senior-financial-analyst-blt951fvvh01be9nvck_en</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Mid-level Calypso Business Analyst</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>https://careers.epam.com/en/vacancy/mid-level-calypso-business-analyst-bltdeazs0xwp2w76h4y_en</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analyst in Marketing Analyst Team (#1194)</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Zone3000</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Zone3000</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>https://zone3000.net/vacancies/senior-marketing-analyst-in-marketing-analyst-team---1194-</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Проектний аналітик в Третій армійський корпус, від&amp;nbsp;$1000</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ab3/vacancies/363773/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Опис: &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Що потрібно робити:&lt;br /&gt;● вести аналітичні проєкти на всіх етапах;&lt;br /&gt;● визначати потребу в даних: які саме дані потрібні, у яких форматах, зрізах і рівнях&lt;br /&gt;деталізації;&lt;br /&gt;● формулювати аналітичні задачі та вимоги до збору / підготовки інформації;&lt;br /&gt;● ви</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик в YASNO, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/yasno/vacancies/363762/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;YASNO&lt;/strong&gt; — бренд енергопостачальних компаній України, що забезпечують електроенергією, газом та енергоефективними рішеннями 3,3 млн сімей і понад 90 тис бізнесів.&lt;br /&gt;Ми бачимо український енергоринок як активного учасника, що може створювати цінність, тому формуємо екосистему прод</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Аналітик процесів в UKRSIBTECH, Київ</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/ukrsibbank/vacancies/363753/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;ПРО НАС&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;UKRSIBBANK BNP Paribas Group — один з найбільших універсальних банків України. Ми об’єднуємо досвід та креативність у своїй команді, створюючи відкрите та інклюзивне середовище для розвитку кожного працівника.&lt;/p&gt;&lt;p&gt;Наші цінності — це відданість, інновації та відкри</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analyst in Marketing Analyst Team (#1194) в ZONE3000, віддалено</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/zone3000/vacancies/363749/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;b&gt;Location: Remote&lt;/b&gt;&lt;/p&gt;&lt;p&gt;&lt;b&gt;Your expertise:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;5+ years in marketing, growth or analytics&lt;/li&gt;&lt;li&gt;Strong SQL for querying and combining data from multiple sources&lt;/li&gt;&lt;li&gt;Proficiency with a BI / visualization tool (preferably Tableau)&lt;/li&gt;&lt;li&gt;Expert Excel/Sheets for modeling and </t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Middle Product Analyst (Growth direction) в appflame, Київ, віддалено</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/appflame/vacancies/363744/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Empowered&lt;/strong&gt; is a PWA platform helping women build better relationships — with themselves and their partners. Personalized courses, self-reflection tools, and expert chats, built around a subscription and transaction model.&lt;/p&gt;&lt;p&gt;We’re hiring the first dedicated analyst on the produ</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Product Analyst в Quarks, Київ, гібрид, Київ, Варшава (Польща), віддалено</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/quarks-tech/vacancies/352129/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Привіт, давай знайомитись ближче.&lt;/p&gt;&lt;p&gt;Ми — &lt;a href="https://quarks.tech/" target="_blank"&gt;&lt;strong&gt;Quarks&lt;/strong&gt;&lt;/a&gt;, технологічна компанія, що створює нішеві продукти у сфері Social Discovery &amp;amp; Relationship Wellness. Фокусуємось на розробці безпечних та ефективних рішень для знайомств і р</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager в Око Камера, Київ</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Привіт! Ми — «Око Камера», українська компанія, що розробляє та виготовляє тепловізійні камери для безпілотників, зокрема БпЛА, НРК та навігаційних систем, заснована у 2022 році. Наші камери перевірені в бою та активно використовуються на фронті для розвідки та цілевказання за поганої видимості а</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Marketing Manager в BLYSKAVKA, $1000–1200, Київ</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/blyskavka/vacancies/363728/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;b&gt;Marketing Manager &lt;/b&gt;&lt;/p&gt;&lt;p&gt;&lt;b&gt;MilTech-компанія | Україна | NDA&lt;/b&gt;&lt;/p&gt;&lt;p&gt;Ми — команда, яка створює продукт, що реально змінює ситуацію на полі бою.&lt;/p&gt;&lt;p&gt;Ми розробляємо та серійно виробляємо сертифікований MilTech-продукт, який вже пройшов перевірку в реальних умовах і стабільно затребуваний</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Аналітик</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834231-analitik/</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Вимоги:&lt;/strong&gt;&lt;br /&gt;&lt;br /&gt;Розвинені аналітичні здібності та системне мислення&lt;br /&gt;Вміння працювати з великими масивами даних&lt;br /&gt;Впевнене володіння MS Office (Excel — обов’язково)&lt;br /&gt;Досвід роботи з Power BI&lt;br /&gt;Знання SQL та/або Python буде перевагою&lt;br /&gt;Уважність до деталей та в</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager/Head of Growth</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834220-growth-marketing-manager-head-of-growth/</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;We are looking for a &lt;strong&gt;Growth Marketing Manager/Head of Growth &lt;/strong&gt;to become the right hand of our CMO and build a scalable lead generation engine from the ground up.&lt;/p&gt;&lt;p&gt;This role combines &lt;strong&gt;performance marketing, website development, and project management&lt;/strong&gt;. You will </t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>System / Business Analyst</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834183-system-business-analyst/</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;E-docs.ua&amp;nbsp;— &lt;/strong&gt;система електронного документообігу та&amp;nbsp;автоматизації документ-орієнтованих процесів в&amp;nbsp;середніх та&amp;nbsp;великих підприємствах. Для компаній ми&amp;nbsp;впровадили та&amp;nbsp;налаштували стандартні процеси&amp;nbsp;— кадрові, господарські, договірні, а&amp;nbsp;також сп</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/832715-data-analyst/</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;📌 Про роль&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ми шукаємо Дата-аналітика для роботи в рамках цифровізації армії. Ваша роль — перетворювати сирі дані на зрозумілі інсайти для бізнесу: від збору й очищення до побудови аналітичних звітів і дашбордів. Ви будете ключовою ланкою між даними й рішеннями.&lt;/p&gt;&lt;p&gt;&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/832718-business-analyst/</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;📌 Про роль&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Шукаємо досвідченого Бізнес-аналітика для виконання повного циклу робіт із збору, аналізу, формалізації, погодження та супроводу бізнес-вимог у межах проекту цифровізації армії. Ви будете сполучною ланкою між бізнесом і технічними командами, перетворюючи потреби </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F725"/>
+  <dimension ref="A1:F739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23602,6 +23602,454 @@
       <c r="F725" t="inlineStr">
         <is>
           <t>2026-06-26 15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>softserve_b8a2c1b3a0bb</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Lead Business Analyst (Data Focus)</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/lead-business-analyst-data-focus-89319</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>DXC_83d249913175</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Business Analyst – Analytics &amp; Business Intelligence Solutions - NJ</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/USA---NJ---NEWARK/Business-Analyst---Analytics---Business-Intelligence-Solutions_51582759</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>whitebit_69a5b5995110</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Financial Manager for Analytics and Control</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1129</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>whitebit_4588e674d3f0</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Growth Manager (Investment Product)</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1144</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>whitebit_3eb71f6293a2</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1170</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>whitebit_a113c1ecd3ca</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Senior Influence Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1171</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>whitebit_fb2fcd534b0f</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Financial Analyst EU</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1204</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>whitebit_884d79963bd8</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Investment Research Analyst</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1160</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834261-junior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Junior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834261-junior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834024-technical-business-analyst-ai-focused/</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Technical Business Analyst (AI-Focused)</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834024-technical-business-analyst-ai-focused/</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834257-business-analyst-workflow-architect-ai-conten/</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Business Analyst / Workflow Architect (AI Content Production)</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834257-business-analyst-workflow-architect-ai-conten/</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834236-credit-risk-analyst/</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Credit Risk Analyst</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834236-credit-risk-analyst/</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/827919-product-analyst/</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827919-product-analyst/</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834252-digital-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834252-digital-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
         </is>
       </c>
     </row>
@@ -23616,7 +24064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F725"/>
+  <dimension ref="A1:F739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -46652,6 +47100,424 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Lead Business Analyst (Data Focus)</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>https://career.softserveinc.com/en-us/vacancies/lead-business-analyst-data-focus-89319</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Business Analysis | Ukraine</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Business Analyst – Analytics &amp; Business Intelligence Solutions - NJ</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>https://dxctechnology.wd1.myworkdayjobs.com/dxcjobs/job/USA---NJ---NEWARK/Business-Analyst---Analytics---Business-Intelligence-Solutions_51582759</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>USA - NJ - NEWARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Financial Manager for Analytics and Control</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1129</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Growth Manager (Investment Product)</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1144</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1170</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Senior Influence Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Financial Analyst EU</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1204</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Investment Research Analyst</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>WhiteBit</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>https://whitebit.hurma.work/public-vacancies/1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Junior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834261-junior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;PlantIn&amp;nbsp;&lt;/strong&gt;— продуктова IT-компанія з екосистеми Genesis, що зближує користувачів з їхніми захопленнями шляхом створення продуктів на основі Machine Learning. Наші застосунки об’єднують понад 55 млн людей у всьому світі.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Переходь на наш сайт, щоб дізнатися більше пр</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:35</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Technical Business Analyst (AI-Focused)</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834024-technical-business-analyst-ai-focused/</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Lynx Trading Technologies&lt;/strong&gt; is the technical infrastructure provider powering institutional trading in U.S. equity markets. We build sophisticated trading technology—think order routing engines, risk management systems, compliance filters, and real-time market connectivity—for brok</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Business Analyst / Workflow Architect (AI Content Production)</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834257-business-analyst-workflow-architect-ai-conten/</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Формат:&lt;/strong&gt; Full-time / Remote&lt;/p&gt;&lt;p&gt;Про компанію&lt;/p&gt;&lt;p&gt;Шукаємо &lt;strong&gt;Business Analyst / Workflow Architect&lt;/strong&gt;, який допоможе перетворити поточний процес із набору дій окремих людей на прозорий, вимірюваний і масштабований конвеєр.&lt;/p&gt;&lt;p&gt;Чому ця роль важлива&lt;/p&gt;&lt;p&gt;Сьогодні зн</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Credit Risk Analyst</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834236-credit-risk-analyst/</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About RiskSeal&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;RiskSeal is a B2B startup serving fintech clients globally. Our API-first credit risk management platform enables digital banks and consumer lenders to simplify onboarding through data-driven insights.&lt;/p&gt;&lt;p&gt;We are growing rapidly and value colla</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/827919-product-analyst/</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;На&amp;nbsp;звʼязку команда expla 🤟&lt;/p&gt;&lt;p&gt;Ми&amp;nbsp;займаємось &lt;strong&gt;performance-маркетингом&lt;/strong&gt; з&amp;nbsp;2015&amp;nbsp;року. Якщо просто: ми&amp;nbsp;допомагаємо великим IT-продуктам знаходити «своїх» людей по&amp;nbsp;всьому світу. Ми&amp;nbsp;не&amp;nbsp;дуже любимо гучні епітети, але цифри кажуть, що&amp;nbsp;ми&amp;nbsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834252-digital-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;We are a friendly team of passionate professionals committed to delivering reliable software solutions for customers from all around the world and we are currently in need of an experienced &lt;strong&gt;Digital Marketing Manager&lt;/strong&gt; &amp;nbsp;to join our team.&lt;br /&gt;What we are missing is you!&lt;br /&gt;&lt;b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F739"/>
+  <dimension ref="A1:F746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24050,6 +24050,230 @@
       <c r="F739" t="inlineStr">
         <is>
           <t>2026-06-26 21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>iDeals_02b8cd998f53</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst / Performance Insights</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>iDeals</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ideals/6f5362bc-433a-4045-97aa-0f2c5d04e525</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>iDeals</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?1782553647</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP) в Wild Hornets Company, Київ</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/mate-academy/vacancies/363799/?1782557464</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager в Mate academy, Київ</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mate-academy/vacancies/363799/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?1782483839</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager в Око Камера, Київ</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834278-senior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834278-senior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834277-senior-business-analyst-partner-platform-paym/</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (Partner Platform / Payments)</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834277-senior-business-analyst-partner-platform-paym/</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834272-business-analyst-odoo-erp/</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP)</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834272-business-analyst-odoo-erp/</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F739"/>
+  <dimension ref="A1:F746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -47518,6 +47742,225 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst / Performance Insights</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>iDeals</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>iDeals</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ideals/6f5362bc-433a-4045-97aa-0f2c5d04e525</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP) в Wild Hornets Company, Київ</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Дикі Шершні (Wild Hornets) &lt;/strong&gt;— українська miltech-компанія, що створює технології, які щодня працюють на фронті. Наші системи використовуються підрозділами ЗСУ для протидії ворожим безпілотникам та захисту інфраструктури.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Ваші основні завдання:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager в Mate academy, Київ</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/mate-academy/vacancies/363799/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Mate academy&lt;/strong&gt; — an EdTech startup with a technological, gamified, AI-powered LMS platform where people learn IT specialties.&lt;/p&gt;&lt;p&gt;🤘Already, &lt;strong&gt;6000+ graduates&lt;/strong&gt; have landed their first IT jobs in just 4 months of training.&lt;/p&gt;&lt;p&gt;🌎 Successfully launched our business in</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager в Око Камера, Київ</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/oko-camera/vacancies/363768/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Привіт! Ми — «Око Камера», українська компанія, що розробляє та виготовляє тепловізійні камери для безпілотників, зокрема БпЛА, НРК та навігаційних систем, заснована у 2022 році. Наші камери перевірені в бою та активно використовуються на фронті для розвідки та цілевказання за поганої видимості а</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834278-senior-product-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Mate academy&lt;/strong&gt; - an EdTech startup with a technological, gamified, AI-powered LMS platform where people learn IT specialties.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;🤘Already, &lt;strong&gt;6000+ graduates&lt;/strong&gt; have landed their first IT jobs in just 4 months of training.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;🌎 Successfull</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (Partner Platform / Payments)</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834277-senior-business-analyst-partner-platform-paym/</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Job Title: Senior Business Analyst (Partner Platform / Payments)&lt;br /&gt;Company: VCG Tech Limited&lt;br /&gt;Location: Remote (Global)&lt;br /&gt;Employment Type: Full-Time&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Role Purpose&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;You will own the requirements, data and acceptance layer for one of our core produc</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP)</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834272-business-analyst-odoo-erp/</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ми&amp;nbsp;шукаємо &lt;strong&gt;досвідченого Business Analyst (Odoo ERP)&lt;/strong&gt;, який допоможе у забезпеченні якісного збору, аналізу, опису та узгодження бізнес-вимог між підрозділами компанії та командою інтегратора ERP-системи&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Ваші основні завдання:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F746"/>
+  <dimension ref="A1:F748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24274,6 +24274,70 @@
       <c r="F746" t="inlineStr">
         <is>
           <t>2026-06-27 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/tscafu/vacancies/334903/?1782565216</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик в Центр Масштабування Технологічних Рішень, $500</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/tscafu/vacancies/334903/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?1782553648</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP) в Wild Hornets Company, Київ</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:35</t>
         </is>
       </c>
     </row>
@@ -24288,7 +24352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F746"/>
+  <dimension ref="A1:F748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -47961,6 +48025,70 @@
         </is>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:35</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Бізнес-аналітик в Центр Масштабування Технологічних Рішень, $500</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/tscafu/vacancies/334903/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Центр масштабування технологічних рішень шукає бізнес-аналітика. Прийом цивільних на військову службу за контрактом.&lt;/p&gt;&lt;p&gt;Обов’язки&lt;/p&gt;&lt;ul&gt;&lt;li&gt;збір, аналіз та документування функціональних і нефункціональних вимог&lt;/li&gt;&lt;li&gt;узгодження вимог між технічною командою і бізнес-стейкхолдерами&lt;/li&gt;&lt;li&gt;пі</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:35</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Business Analyst(Odoo ERP) в Wild Hornets Company, Київ</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/wild-hornets-company/vacancies/363797/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Дикі Шершні (Wild Hornets) &lt;/strong&gt;— українська miltech-компанія, що створює технології, які щодня працюють на фронті. Наші системи використовуються підрозділами ЗСУ для протидії ворожим безпілотникам та захисту інфраструктури.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Ваші основні завдання:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F748"/>
+  <dimension ref="A1:F750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24338,6 +24338,70 @@
       <c r="F748" t="inlineStr">
         <is>
           <t>2026-06-27 15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/812332-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Marketing manager</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/812332-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>2026-06-28 06:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/829614-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/829614-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>2026-06-28 06:38</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F748"/>
+  <dimension ref="A1:F750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -48089,6 +48153,70 @@
         </is>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-06-28 06:38</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Marketing manager</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/812332-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;У зв'язку з розвитком проектів шукаємо Marketing manager, який/яка буде розробляти та впроваджувати ефективні маркетингові кампанії для підвищення впізнаваності бренду, зміцнення його репутації та залучення нових читачів, одночасно забезпечуючи підтримку позитивного іміджу компанії через активну </t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-06-28 06:38</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Growth Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/829614-growth-marketing-manager/</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Ligamedia&lt;/strong&gt;&amp;nbsp;— медіахолдинг, створений для об'єднання та розвитку існуючих і нових видів діяльності. Сьогодні Ligamedia об'єднує портал LIGA.net, рекламне агентство ADLOVE, LIGAclub, прес-центр та інформаційне агентство ЛігаБізнесІнформ. В рамках Ligamedia, також існує компанія</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F750"/>
+  <dimension ref="A1:F751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24402,6 +24402,38 @@
       <c r="F750" t="inlineStr">
         <is>
           <t>2026-06-28 06:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834292-people-analyst/</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>People Analyst</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834292-people-analyst/</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2026-06-28 09:28</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F750"/>
+  <dimension ref="A1:F751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -48217,6 +48249,38 @@
         </is>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-06-28 09:28</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>People Analyst</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834292-people-analyst/</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Шукаємо HR Analyst, який відповідатиме за побудову системної HR-аналітики, розвиток Power BI dashboards, формування HR Metrics Book, регулярну управлінську звітність, risk map, ad hoc analytics та підготовку аналітичних висновків для бізнесу.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Основні обов’язки&lt;/strong&gt;&lt;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seen_jobs.xlsx
+++ b/seen_jobs.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F751"/>
+  <dimension ref="A1:F754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24434,6 +24434,102 @@
       <c r="F751" t="inlineStr">
         <is>
           <t>2026-06-28 09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>dou_https://jobs.dou.ua/companies/7-korpus-dsv/vacancies/350241/?1782650411</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Дата-аналітик в 7 Корпус Швидкого Реагування Десантно-штурмових військ, $500–1500</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/7-korpus-dsv/vacancies/350241/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834304-product-analyst-product-operations-analyst-ap/</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Product Analyst / Product Operations Analyst — API Integrations</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834304-product-analyst-product-operations-analyst-ap/</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>djinni_https://djinni.co/jobs/834299-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик / Фінансист</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834299-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F751"/>
+  <dimension ref="A1:F754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -48281,6 +48377,102 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Дата-аналітик в 7 Корпус Швидкого Реагування Десантно-штурмових військ, $500–1500</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>DOU</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>DOU.ua</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>https://jobs.dou.ua/companies/7-korpus-dsv/vacancies/350241/?utm_source=jobsrss</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Привіт! Ми — 7 корпус швидкого реагування Десантно-штурмових військ Збройних Сил України, де поєднуються мужність, професіоналізм і найсучасніші технології. Наш технодесант — це новий рівень розвитку, який вимагає від кожного бути не лише воїном, а й експертом у використанні інноваційних рішень. </t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Product Analyst / Product Operations Analyst — API Integrations</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834304-product-analyst-product-operations-analyst-ap/</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Agave is looking for a sharp, semi-technical Product Analyst / Product Operations Analyst with 0–2 years of experience to become a deep product expert and help us scale.&lt;/p&gt;&lt;p&gt;This is an execution-focused role for someone who enjoys diving into API documentation, understanding technical edge case</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:32</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Фінансовий аналітик / Фінансист</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Djinni</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Djinni.co</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>https://djinni.co/jobs/834299-finansovii-analitik-finansist/</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Локація: Варшава&lt;br /&gt;Формат роботи: віддалено (у перспективі — гібрид)&lt;br /&gt;Зайнятість: part-time (на старті)&lt;br /&gt;Заробітна плата: $500–700&lt;br /&gt;Графік: 10:00–14:00 або інший слот у проміжку 10:00–19:00&lt;/p&gt;&lt;p&gt;Шукаємо фінансового аналітика / фінансиста, який допоможе з фінансовим обліком, звітні</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
